--- a/ProjectProgress/表格/分类进展/性能问题.xlsx
+++ b/ProjectProgress/表格/分类进展/性能问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能问题" sheetId="1" r:id="Rf90bc615eaf34284"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能问题" sheetId="1" r:id="Rc00d2592548743fd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress8" displayName="CategoryProgress8" ref="A7:H12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H12"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress8" displayName="CategoryProgress8" ref="A7:H17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H17"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-09-30 17:14:21（北京时间）</x:v>
+        <x:v>更新于 2026-10-01 09:11:08（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,23 +464,23 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C12,A5)</x:f>
-        <x:v>3</x:v>
+        <x:f>COUNTIF(C8:C17,A5)</x:f>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C12,D5)</x:f>
+        <x:f>COUNTIF(C8:C17,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C12,F5)</x:f>
-        <x:v>2</x:v>
+        <x:f>COUNTIF(C8:C17,F5)</x:f>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
     </x:row>
@@ -520,31 +520,31 @@
         <x:v>用户备注</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="75" customHeight="1">
+    <x:row r="8" ht="126" customHeight="1">
       <x:c r="A8" s="7" t="str">
         <x:v>CA-026.02</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>缓存与阴影容量警告优化范围</x:v>
+        <x:v>非 Nanite 阴影队列溢出与预算范围</x:v>
       </x:c>
       <x:c r="C8" s="18" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>教学楼 B 发黑已在原缓存设置下修复；Lumen 缓存与阴影容量性能警告仍未由该修复解决。固定视角关闭阴影仅约 24→25 FPS。</x:v>
+        <x:v>9 月 30 日日志确认两次非 Nanite VSM 队列溢出。远景森林、圆庭铺装和新增植被为分区测量候选，资产规模不等于每帧实际绘制量；当前镜头主要受 CPU 限制。旧体育馆植物 Lumen 尖峰已有修复，不能重复认定为当前瓶颈。</x:v>
       </x:c>
       <x:c r="E8" s="7" t="str">
-        <x:v>结合当前运行记录确认警告是否仍存在、影响哪些路线及拟优化范围。</x:v>
+        <x:v>确认阴影预算及分区优化范围；方案尚未实施，需以各区域 A/B 和运行路线证明收益。其他历史缓存警告仍需当前证据，不能推定全部解决。</x:v>
       </x:c>
       <x:c r="F8" s="14" t="n">
-        <x:v>46292</x:v>
+        <x:v>46295</x:v>
       </x:c>
       <x:c r="G8" s="7" t="str">
-        <x:v>发黑修复剩余警告与阴影实测</x:v>
+        <x:v>scene 性能排查报告第 4、6 节及聊天最终结果</x:v>
       </x:c>
       <x:c r="H8" s="16" t="str"/>
     </x:row>
-    <x:row r="9" ht="75" customHeight="1">
+    <x:row r="9" ht="109" customHeight="1">
       <x:c r="A9" s="7" t="str">
         <x:v>CA-026.03</x:v>
       </x:c>
@@ -555,132 +555,252 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>当前只确认局部帧耗与编辑器固定视角结果；尚无统一目标帧率、画质档位、硬件及全校园验收路线证据。</x:v>
+        <x:v>已知测试机器为 Ryzen 5700X、RTX 4060 Ti、16 GB 内存，当前固定编辑器镜头为 Epic 质量，340 帧整帧中位 38.54 ms。报告中的 60 FPS 仅为假设，用户尚未指定目标，也未验收打包版本或统一内部分辨率。</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>确认目标帧率、硬件、画质和运行方式，再确定是否达标及优化优先级。</x:v>
+        <x:v>确认交付帧率、目标硬件、内部分辨率、画质、编辑器或打包运行方式和校园验收路线；当前基准不能证明整体达标。</x:v>
       </x:c>
       <x:c r="F9" s="14" t="n">
         <x:v>46295</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
-        <x:v>阴影实测限制及近期项目进展范围</x:v>
+        <x:v>scene 性能排查报告第 1、7 节：实测条件与目标限制</x:v>
       </x:c>
       <x:c r="H9" s="16" t="str"/>
     </x:row>
     <x:row r="10" ht="109" customHeight="1">
       <x:c r="A10" s="7" t="str">
+        <x:v>CA-032.02</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="str">
+        <x:v>编辑器 TEDS 层级解析等待优化范围</x:v>
+      </x:c>
+      <x:c r="C10" s="18" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="D10" s="7" t="str">
+        <x:v>309/309 个 Mass Tick 对应 resolver worker；时间并集覆盖主线程 Mass 包络 97.74%，约 28.86 ms/帧。热点链路已定位，但具体未解析父行、hierarchy 和关闭 TEDS 的收益尚未实测。</x:v>
+      </x:c>
+      <x:c r="E10" s="7" t="str">
+        <x:v>用户本次要求只排查。是否实施启动配置 A/B、父映射审计或增量解析仍需决定；不能直接认定引擎缺陷或承诺可消除全部等待。</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="G10" s="7" t="str">
+        <x:v>性能排查报告第 2 节：逐帧任务关联与限制</x:v>
+      </x:c>
+      <x:c r="H10" s="16" t="str"/>
+    </x:row>
+    <x:row r="11" ht="109" customHeight="1">
+      <x:c r="A11" s="7" t="str">
+        <x:v>CA-032.03</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="str">
+        <x:v>全场无变化 ISM 同步与启动等待</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="D11" s="7" t="str">
+        <x:v>当前 9,408 组全部 unchanged、0 created，同步仍耗时 135.11 秒，其中 scan 115.061 秒；同次 PIE 总启动 157.99 秒。完整同步钩子已核实，脏组追踪、签名缓存和增量校验尚无实施依据。</x:v>
+      </x:c>
+      <x:c r="E11" s="7" t="str">
+        <x:v>确认是否采用增量同步方案；需分别验证无变化、单组变更、撤销和引用变化。CA-025.02 为已完成的旧内部读取阶段，不能替代本项。</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="G11" s="7" t="str">
+        <x:v>性能排查报告第 3 节：日志与同步钩子</x:v>
+      </x:c>
+      <x:c r="H11" s="16" t="str"/>
+    </x:row>
+    <x:row r="12" ht="92" customHeight="1">
+      <x:c r="A12" s="7" t="str">
+        <x:v>CA-032.04</x:v>
+      </x:c>
+      <x:c r="B12" s="7" t="str">
+        <x:v>冷启动 PSO 卡顿和预缓存覆盖</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="D12" s="7" t="str">
+        <x:v>日志累计记录 50 次 PSO 创建 hitch，15 graphics、35 compute，0 precached。未把这些累计事件等同于当前短采样中的每个长帧；目标运行版本尚未复核。</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="str">
+        <x:v>确认是否开展目标版本的冷启动、预缓存和首条路线预热验证，再决定实施范围。</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="G12" s="7" t="str">
+        <x:v>性能排查报告第 5 节：PSO 累计日志边界</x:v>
+      </x:c>
+      <x:c r="H12" s="16" t="str"/>
+    </x:row>
+    <x:row r="13" ht="75" customHeight="1">
+      <x:c r="A13" s="7" t="str">
+        <x:v>CA-032.05</x:v>
+      </x:c>
+      <x:c r="B13" s="7" t="str">
+        <x:v>高复杂度导航碰撞实际开销复核</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="D13" s="7" t="str">
+        <x:v>导航导出发现约 259,200 和 201,376 三角的两处高复杂度碰撞。报告仅列出风险和简化候选，尚未测清生成时序与运行帧耗影响。</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="str">
+        <x:v>确认是否测导航生成时序和可行走范围；仅在影响被验证后决定碰撞简化，不能把复杂度直接当作已复现帧率主因。</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="G13" s="7" t="str">
+        <x:v>性能排查报告第 5 节：导航候选与未验证影响</x:v>
+      </x:c>
+      <x:c r="H13" s="16" t="str"/>
+    </x:row>
+    <x:row r="14" ht="109" customHeight="1">
+      <x:c r="A14" s="7" t="str">
         <x:v>CA-025</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="str">
+      <x:c r="B14" s="7" t="str">
         <x:v>体育馆道路植物 Nanite 配置及短时性能改善</x:v>
       </x:c>
-      <x:c r="C10" s="20" t="str">
+      <x:c r="C14" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="D10" s="7" t="str">
+      <x:c r="D14" s="7" t="str">
         <x:v>11 类优化网格和 54 个材质/父材质资源用于 9,369 个实例，变换与属性校验通过。
 相同视角 GPU 均值：30.57 → 16.35 ms。
 四组共 1,654 帧无超过 100 ms 的长帧，原始资产保留。</x:v>
       </x:c>
-      <x:c r="E10" s="7" t="str">
+      <x:c r="E14" s="7" t="str">
         <x:v>该阶段完成范围为短时编辑器测试；常态约43–45ms，未证明60FPS、打包版或长时间目标达成。</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="n">
+      <x:c r="F14" s="14" t="n">
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="G10" s="7" t="str">
+      <x:c r="G14" s="7" t="str">
         <x:v>体育馆道路优化实测与完整性记录</x:v>
       </x:c>
-      <x:c r="H10" s="16" t="str"/>
-    </x:row>
-    <x:row r="11" ht="92" customHeight="1">
-      <x:c r="A11" s="7" t="str">
+      <x:c r="H14" s="16" t="str"/>
+    </x:row>
+    <x:row r="15" ht="126" customHeight="1">
+      <x:c r="A15" s="7" t="str">
         <x:v>CA-025.02</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="str">
+      <x:c r="B15" s="7" t="str">
         <x:v>保存和 PIE 同步内部读取优化</x:v>
       </x:c>
-      <x:c r="C11" s="20" t="str">
+      <x:c r="C15" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="D11" s="7" t="str">
-        <x:v>在保持全场完整扫描的前提下合并属性读取并复用同次同步的解析；实际保存同步180.87→145.68秒，10,264批次及110,462实例保持，9项回归与语法检查通过。</x:v>
-      </x:c>
-      <x:c r="E11" s="7" t="str">
-        <x:v>保存仍有全场扫描等待；后续若改同步策略，以实际保存和完整性证据复核。</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="n">
-        <x:v>46285</x:v>
-      </x:c>
-      <x:c r="G11" s="7" t="str">
-        <x:v>同步优化测试及实际保存测量</x:v>
-      </x:c>
-      <x:c r="H11" s="16" t="str"/>
-    </x:row>
-    <x:row r="12" ht="92" customHeight="1">
-      <x:c r="A12" s="7" t="str">
+      <x:c r="D15" s="7" t="str">
+        <x:v>9 月 20 日保持全场完整扫描的内部读取优化已交付，实际保存同步由 180.87 降至 145.68 秒，10,264 批次和 110,462 实例保持，引用与语法检查通过。9 月 30 日当前场景无变化同步仍为 135.11 秒；旧阶段交付仍有效，增量同步缺口另见 CA-032.03。</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="str">
+        <x:v>保留该阶段优化依据。当前无变化同步和启动等待按 CA-032.03 独立跟踪，不能据此宣称整体同步性能达标。</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="G15" s="7" t="str">
+        <x:v>历史内部读取优化结果与 scene 当前完整扫描报告</x:v>
+      </x:c>
+      <x:c r="H15" s="16" t="str"/>
+    </x:row>
+    <x:row r="16" ht="92" customHeight="1">
+      <x:c r="A16" s="7" t="str">
         <x:v>CA-026</x:v>
       </x:c>
-      <x:c r="B12" s="7" t="str">
+      <x:c r="B16" s="7" t="str">
         <x:v>固定视角阴影性能基线测量</x:v>
       </x:c>
-      <x:c r="C12" s="20" t="str">
+      <x:c r="C16" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="D12" s="7" t="str">
+      <x:c r="D16" s="7" t="str">
         <x:v>RTX 4060 Ti 固定编辑器视角开—关—开各 180 帧采样，阴影净 GPU 开销约 2.14 ms/帧、11.8%，显存差约 522 MiB；所有临时设置已恢复。</x:v>
       </x:c>
-      <x:c r="E12" s="7" t="str">
+      <x:c r="E16" s="7" t="str">
         <x:v>把此结果作为固定视角基线；其他视角和实际运行需分别测量。</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="n">
+      <x:c r="F16" s="14" t="n">
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="G12" s="7" t="str">
+      <x:c r="G16" s="7" t="str">
         <x:v>阴影开销实测：有效绘制采样</x:v>
       </x:c>
-      <x:c r="H12" s="16" t="str"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="1"/>
-      <x:c r="B13" s="1"/>
-      <x:c r="C13" s="1"/>
-      <x:c r="D13" s="1"/>
-      <x:c r="E13" s="1"/>
-      <x:c r="F13" s="1"/>
-      <x:c r="G13" s="1"/>
-      <x:c r="H13" s="1"/>
-    </x:row>
-    <x:row r="14" ht="34" customHeight="1">
-      <x:c r="A14" s="3" t="str">
+      <x:c r="H16" s="16" t="str"/>
+    </x:row>
+    <x:row r="17" ht="126" customHeight="1">
+      <x:c r="A17" s="7" t="str">
+        <x:v>CA-032</x:v>
+      </x:c>
+      <x:c r="B17" s="7" t="str">
+        <x:v>scene 当前性能诊断报告交付</x:v>
+      </x:c>
+      <x:c r="C17" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D17" s="7" t="str">
+        <x:v>受控固定编辑器镜头采集 360 帧，取内部 340 帧。整帧中位 38.54 ms、主线程 38.47 ms、GPU 13.01 ms；CPU trace 定位 TEDS 层级解析等待。报告已保存，并按用户要求上传 main，提交 ce7ce0f631f9fc97c2c426d35fa0abfff5abae6e。</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="str">
+        <x:v>本阶段仅诊断和方案交付。实施范围分别见 CA-032.02 至 CA-032.05、CA-026.02；整体目标见 CA-026.03。</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="G17" s="7" t="str">
+        <x:v>性能排查聊天最终交付、报告与受控指标</x:v>
+      </x:c>
+      <x:c r="H17" s="16" t="str"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="1"/>
+      <x:c r="B18" s="1"/>
+      <x:c r="C18" s="1"/>
+      <x:c r="D18" s="1"/>
+      <x:c r="E18" s="1"/>
+      <x:c r="F18" s="1"/>
+      <x:c r="G18" s="1"/>
+      <x:c r="H18" s="1"/>
+    </x:row>
+    <x:row r="19" ht="34" customHeight="1">
+      <x:c r="A19" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B14" s="21" t="str">
+      <x:c r="B19" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C14" s="21"/>
-      <x:c r="D14" s="21"/>
-      <x:c r="E14" s="21"/>
-      <x:c r="F14" s="21"/>
-      <x:c r="G14" s="21"/>
-      <x:c r="H14" s="21"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="1"/>
-      <x:c r="B15" s="1"/>
-      <x:c r="C15" s="1"/>
-      <x:c r="D15" s="1"/>
-      <x:c r="E15" s="1"/>
-      <x:c r="F15" s="1"/>
-      <x:c r="G15" s="1"/>
-      <x:c r="H15" s="1"/>
+      <x:c r="C19" s="21"/>
+      <x:c r="D19" s="21"/>
+      <x:c r="E19" s="21"/>
+      <x:c r="F19" s="21"/>
+      <x:c r="G19" s="21"/>
+      <x:c r="H19" s="21"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="1"/>
+      <x:c r="B20" s="1"/>
+      <x:c r="C20" s="1"/>
+      <x:c r="D20" s="1"/>
+      <x:c r="E20" s="1"/>
+      <x:c r="F20" s="1"/>
+      <x:c r="G20" s="1"/>
+      <x:c r="H20" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B14:H14"/>
+    <x:mergeCell ref="B19:H19"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C12">
+  <x:conditionalFormatting sqref="C8:C17">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -692,13 +812,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C12">
+    <x:dataValidation type="list" sqref="C8:C17">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racc0864a113f4f9c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R758aed5b7dba4b0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/性能问题.xlsx
+++ b/ProjectProgress/表格/分类进展/性能问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能问题" sheetId="1" r:id="Rc00d2592548743fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能问题" sheetId="1" r:id="R3c81e81c57204f12"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress8" displayName="CategoryProgress8" ref="A7:H17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress8" displayName="CategoryProgress8" ref="A7:H23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H23"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-01 09:11:08（北京时间）</x:v>
+        <x:v>更新于 2026-10-03 09:09:53（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,23 +464,23 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C17,A5)</x:f>
-        <x:v>4</x:v>
+        <x:f>COUNTIF(C8:C23,A5)</x:f>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C17,D5)</x:f>
+        <x:f>COUNTIF(C8:C23,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C17,F5)</x:f>
-        <x:v>6</x:v>
+        <x:f>COUNTIF(C8:C23,F5)</x:f>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
     </x:row>
@@ -531,20 +531,20 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>9 月 30 日日志确认两次非 Nanite VSM 队列溢出。远景森林、圆庭铺装和新增植被为分区测量候选，资产规模不等于每帧实际绘制量；当前镜头主要受 CPU 限制。旧体育馆植物 Lumen 尖峰已有修复，不能重复认定为当前瓶颈。</x:v>
+        <x:v>历史日志有非Nanite VSM工作队列溢出。10月3日已按用户选择在188个远景组件关闭投影并禁用Nanite，32,598个原投影实例受影响，保存回读通过。没有修改后同视角A/B、警告日志或运行路线复测，不能判定队列溢出及性能目标已解决。</x:v>
       </x:c>
       <x:c r="E8" s="7" t="str">
-        <x:v>确认阴影预算及分区优化范围；方案尚未实施，需以各区域 A/B 和运行路线证明收益。其他历史缓存警告仍需当前证据，不能推定全部解决。</x:v>
+        <x:v>设置交付见 CA-041、CA-041.02，持久化见 CA-041.03。确认修改后VSM警告和同口径性能结果；光追几何池问题独立见 CA-042。</x:v>
       </x:c>
       <x:c r="F8" s="14" t="n">
-        <x:v>46295</x:v>
+        <x:v>46298</x:v>
       </x:c>
       <x:c r="G8" s="7" t="str">
-        <x:v>scene 性能排查报告第 4、6 节及聊天最终结果</x:v>
+        <x:v>最新远景修复保存交付与VSM历史诊断</x:v>
       </x:c>
       <x:c r="H8" s="16" t="str"/>
     </x:row>
-    <x:row r="9" ht="109" customHeight="1">
+    <x:row r="9" ht="126" customHeight="1">
       <x:c r="A9" s="7" t="str">
         <x:v>CA-026.03</x:v>
       </x:c>
@@ -555,16 +555,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>已知测试机器为 Ryzen 5700X、RTX 4060 Ti、16 GB 内存，当前固定编辑器镜头为 Epic 质量，340 帧整帧中位 38.54 ms。报告中的 60 FPS 仅为假设，用户尚未指定目标，也未验收打包版本或统一内部分辨率。</x:v>
+        <x:v>已知测试机器 Ryzen 5700X、RTX 4060 Ti、16 GB 系统内存。10 月 2 日 Shipping 诊断包固定视点实测 39.45 应用 FPS，但实际显示帧率和后缓冲像素数未确认。60 FPS 仍为报告假设，用户未指定目标；正常发布构建尚未通过。</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>确认交付帧率、目标硬件、内部分辨率、画质、编辑器或打包运行方式和校园验收路线；当前基准不能证明整体达标。</x:v>
+        <x:v>确认交付帧率、硬件、画质、内部分辨率和验收路线。实测基准 CA-037 不等于总体达标；发布与像素验收见 CA-038.02、CA-038.03。</x:v>
       </x:c>
       <x:c r="F9" s="14" t="n">
-        <x:v>46295</x:v>
+        <x:v>46297</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
-        <x:v>scene 性能排查报告第 1、7 节：实测条件与目标限制</x:v>
+        <x:v>Shipping 报告第 1、4、6 节：测试条件、成绩与目标边界</x:v>
       </x:c>
       <x:c r="H9" s="16" t="str"/>
     </x:row>
@@ -616,7 +616,7 @@
       </x:c>
       <x:c r="H11" s="16" t="str"/>
     </x:row>
-    <x:row r="12" ht="92" customHeight="1">
+    <x:row r="12" ht="109" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>CA-032.04</x:v>
       </x:c>
@@ -627,16 +627,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D12" s="7" t="str">
-        <x:v>日志累计记录 50 次 PSO 创建 hitch，15 graphics、35 compute，0 precached。未把这些累计事件等同于当前短采样中的每个长帧；目标运行版本尚未复核。</x:v>
+        <x:v>编辑器日志历史有 50 次 PSO hitch、0 precached。Shipping 第二次启动记录 907.06 和 414.06 ms 长帧，未清 OS/驱动缓存，也未同步 PSO、流送、磁盘或线程事件；不能将长帧直接归因 PSO 或称为真正冷启动。</x:v>
       </x:c>
       <x:c r="E12" s="7" t="str">
-        <x:v>确认是否开展目标版本的冷启动、预缓存和首条路线预热验证，再决定实施范围。</x:v>
+        <x:v>保留已交付启动观测。冷缓存、预缓存覆盖与长帧时间关联仍缺证据，确认实施或继续诊断范围。</x:v>
       </x:c>
       <x:c r="F12" s="14" t="n">
-        <x:v>46295</x:v>
+        <x:v>46297</x:v>
       </x:c>
       <x:c r="G12" s="7" t="str">
-        <x:v>性能排查报告第 5 节：PSO 累计日志边界</x:v>
+        <x:v>编辑器 PSO 日志及 Shipping 报告第 5、6 节启动边界</x:v>
       </x:c>
       <x:c r="H12" s="16" t="str"/>
     </x:row>
@@ -666,141 +666,285 @@
     </x:row>
     <x:row r="14" ht="109" customHeight="1">
       <x:c r="A14" s="7" t="str">
+        <x:v>CA-037.03</x:v>
+      </x:c>
+      <x:c r="B14" s="7" t="str">
+        <x:v>Shipping 运行时渲染负载根因复核</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="D14" s="7" t="str">
+        <x:v>正式样本整卡 GPU 利用率均值 98.43%、区间 96–99%。尚无逐帧 GPU/GT/RT 或渲染 pass 数据，不能确认 VSM、Lumen 或几何的具体占比，也不能沿用编辑器 TEDS 热点作为 Shipping 根因。</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="str">
+        <x:v>当前仅为高负载线索，根因及优化范围仍待确认；如继续诊断，需相同资产、镜头和画质下的可靠逐帧数据。</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="n">
+        <x:v>46297</x:v>
+      </x:c>
+      <x:c r="G14" s="7" t="str">
+        <x:v>Shipping 报告第 4、6 节资源采样与归因边界</x:v>
+      </x:c>
+      <x:c r="H14" s="16" t="str"/>
+    </x:row>
+    <x:row r="15" ht="92" customHeight="1">
+      <x:c r="A15" s="7" t="str">
+        <x:v>CA-042</x:v>
+      </x:c>
+      <x:c r="B15" s="7" t="str">
+        <x:v>scene光追几何池预算警告</x:v>
+      </x:c>
+      <x:c r="C15" s="18" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="D15" s="7" t="str">
+        <x:v>10月2日聊天确认需求651.9MiB超过400MiB几何池；常驻256.9MiB约占预算64%，另触发20%占比警告。建议1536MiB仅为测试方案，尚无实施或验收依据。</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="str">
+        <x:v>核对是否实施几何池调整及当前警告；400→1024仍可能触发常驻占比警告。后续远景设置交付不证明此问题已解决。</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="n">
+        <x:v>46297</x:v>
+      </x:c>
+      <x:c r="G15" s="7" t="str">
+        <x:v>渲染警告聊天诊断最终结果</x:v>
+      </x:c>
+      <x:c r="H15" s="16" t="str"/>
+    </x:row>
+    <x:row r="16" ht="109" customHeight="1">
+      <x:c r="A16" s="7" t="str">
         <x:v>CA-025</x:v>
       </x:c>
-      <x:c r="B14" s="7" t="str">
+      <x:c r="B16" s="7" t="str">
         <x:v>体育馆道路植物 Nanite 配置及短时性能改善</x:v>
       </x:c>
-      <x:c r="C14" s="20" t="str">
+      <x:c r="C16" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
-      <x:c r="D14" s="7" t="str">
+      <x:c r="D16" s="7" t="str">
         <x:v>11 类优化网格和 54 个材质/父材质资源用于 9,369 个实例，变换与属性校验通过。
 相同视角 GPU 均值：30.57 → 16.35 ms。
 四组共 1,654 帧无超过 100 ms 的长帧，原始资产保留。</x:v>
       </x:c>
-      <x:c r="E14" s="7" t="str">
+      <x:c r="E16" s="7" t="str">
         <x:v>该阶段完成范围为短时编辑器测试；常态约43–45ms，未证明60FPS、打包版或长时间目标达成。</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="n">
+      <x:c r="F16" s="14" t="n">
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="G14" s="7" t="str">
+      <x:c r="G16" s="7" t="str">
         <x:v>体育馆道路优化实测与完整性记录</x:v>
-      </x:c>
-      <x:c r="H14" s="16" t="str"/>
-    </x:row>
-    <x:row r="15" ht="126" customHeight="1">
-      <x:c r="A15" s="7" t="str">
-        <x:v>CA-025.02</x:v>
-      </x:c>
-      <x:c r="B15" s="7" t="str">
-        <x:v>保存和 PIE 同步内部读取优化</x:v>
-      </x:c>
-      <x:c r="C15" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D15" s="7" t="str">
-        <x:v>9 月 20 日保持全场完整扫描的内部读取优化已交付，实际保存同步由 180.87 降至 145.68 秒，10,264 批次和 110,462 实例保持，引用与语法检查通过。9 月 30 日当前场景无变化同步仍为 135.11 秒；旧阶段交付仍有效，增量同步缺口另见 CA-032.03。</x:v>
-      </x:c>
-      <x:c r="E15" s="7" t="str">
-        <x:v>保留该阶段优化依据。当前无变化同步和启动等待按 CA-032.03 独立跟踪，不能据此宣称整体同步性能达标。</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="n">
-        <x:v>46295</x:v>
-      </x:c>
-      <x:c r="G15" s="7" t="str">
-        <x:v>历史内部读取优化结果与 scene 当前完整扫描报告</x:v>
-      </x:c>
-      <x:c r="H15" s="16" t="str"/>
-    </x:row>
-    <x:row r="16" ht="92" customHeight="1">
-      <x:c r="A16" s="7" t="str">
-        <x:v>CA-026</x:v>
-      </x:c>
-      <x:c r="B16" s="7" t="str">
-        <x:v>固定视角阴影性能基线测量</x:v>
-      </x:c>
-      <x:c r="C16" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D16" s="7" t="str">
-        <x:v>RTX 4060 Ti 固定编辑器视角开—关—开各 180 帧采样，阴影净 GPU 开销约 2.14 ms/帧、11.8%，显存差约 522 MiB；所有临时设置已恢复。</x:v>
-      </x:c>
-      <x:c r="E16" s="7" t="str">
-        <x:v>把此结果作为固定视角基线；其他视角和实际运行需分别测量。</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="n">
-        <x:v>46292</x:v>
-      </x:c>
-      <x:c r="G16" s="7" t="str">
-        <x:v>阴影开销实测：有效绘制采样</x:v>
       </x:c>
       <x:c r="H16" s="16" t="str"/>
     </x:row>
     <x:row r="17" ht="126" customHeight="1">
       <x:c r="A17" s="7" t="str">
-        <x:v>CA-032</x:v>
+        <x:v>CA-025.02</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
-        <x:v>scene 当前性能诊断报告交付</x:v>
+        <x:v>保存和 PIE 同步内部读取优化</x:v>
       </x:c>
       <x:c r="C17" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D17" s="7" t="str">
-        <x:v>受控固定编辑器镜头采集 360 帧，取内部 340 帧。整帧中位 38.54 ms、主线程 38.47 ms、GPU 13.01 ms；CPU trace 定位 TEDS 层级解析等待。报告已保存，并按用户要求上传 main，提交 ce7ce0f631f9fc97c2c426d35fa0abfff5abae6e。</x:v>
+        <x:v>9 月 20 日保持全场完整扫描的内部读取优化已交付，实际保存同步由 180.87 降至 145.68 秒，10,264 批次和 110,462 实例保持，引用与语法检查通过。9 月 30 日当前场景无变化同步仍为 135.11 秒；旧阶段交付仍有效，增量同步缺口另见 CA-032.03。</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
-        <x:v>本阶段仅诊断和方案交付。实施范围分别见 CA-032.02 至 CA-032.05、CA-026.02；整体目标见 CA-026.03。</x:v>
+        <x:v>保留该阶段优化依据。当前无变化同步和启动等待按 CA-032.03 独立跟踪，不能据此宣称整体同步性能达标。</x:v>
       </x:c>
       <x:c r="F17" s="14" t="n">
         <x:v>46295</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
-        <x:v>性能排查聊天最终交付、报告与受控指标</x:v>
+        <x:v>历史内部读取优化结果与 scene 当前完整扫描报告</x:v>
       </x:c>
       <x:c r="H17" s="16" t="str"/>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="1"/>
-      <x:c r="B18" s="1"/>
-      <x:c r="C18" s="1"/>
-      <x:c r="D18" s="1"/>
-      <x:c r="E18" s="1"/>
-      <x:c r="F18" s="1"/>
-      <x:c r="G18" s="1"/>
-      <x:c r="H18" s="1"/>
-    </x:row>
-    <x:row r="19" ht="34" customHeight="1">
-      <x:c r="A19" s="3" t="str">
+    <x:row r="18" ht="92" customHeight="1">
+      <x:c r="A18" s="7" t="str">
+        <x:v>CA-026</x:v>
+      </x:c>
+      <x:c r="B18" s="7" t="str">
+        <x:v>固定视角阴影性能基线测量</x:v>
+      </x:c>
+      <x:c r="C18" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D18" s="7" t="str">
+        <x:v>RTX 4060 Ti 固定编辑器视角开—关—开各 180 帧采样，阴影净 GPU 开销约 2.14 ms/帧、11.8%，显存差约 522 MiB；所有临时设置已恢复。</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="str">
+        <x:v>把此结果作为固定视角基线；其他视角和实际运行需分别测量。</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="n">
+        <x:v>46292</x:v>
+      </x:c>
+      <x:c r="G18" s="7" t="str">
+        <x:v>阴影开销实测：有效绘制采样</x:v>
+      </x:c>
+      <x:c r="H18" s="16" t="str"/>
+    </x:row>
+    <x:row r="19" ht="126" customHeight="1">
+      <x:c r="A19" s="7" t="str">
+        <x:v>CA-032</x:v>
+      </x:c>
+      <x:c r="B19" s="7" t="str">
+        <x:v>scene 当前性能诊断报告交付</x:v>
+      </x:c>
+      <x:c r="C19" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D19" s="7" t="str">
+        <x:v>固定编辑器镜头的 340 帧诊断：整帧中位 38.54 ms、主线程 38.47 ms、GPU 13.01 ms，定位 TEDS 等待。10 月 1 日按用户要求转换为 Markdown，结论保留，上传 main 提交 c540e83b047b03ce6476cf720c91eaa6990837b0，替换远端 TXT。</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="str">
+        <x:v>编辑器诊断报告交付有效。Shipping 独立实测见 CA-037，两个环境镜头与采样口径不同，不能计算优化倍率。</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="n">
+        <x:v>46296</x:v>
+      </x:c>
+      <x:c r="G19" s="7" t="str">
+        <x:v>性能聊天 Markdown 格式纠正与上传交付</x:v>
+      </x:c>
+      <x:c r="H19" s="16" t="str"/>
+    </x:row>
+    <x:row r="20" ht="109" customHeight="1">
+      <x:c r="A20" s="7" t="str">
+        <x:v>CA-037</x:v>
+      </x:c>
+      <x:c r="B20" s="7" t="str">
+        <x:v>Shipping 诊断包固定视点性能基准</x:v>
+      </x:c>
+      <x:c r="C20" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D20" s="7" t="str">
+        <x:v>教学楼 A 前同一视点三轮各 60 秒、共 7,095 帧：平均应用 39.45 FPS，P95 34.94 ms，1% low 25.90 FPS；最大 48.26 ms，无 &gt;50 ms 帧。视线转向地面的旧约 60 FPS 样本已排除。</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="str">
+        <x:v>基准阶段已完成，仅代表本机、诊断包与该视点。总体目标见 CA-026.03，标准发布和实际显示验收见 CA-038.02、CA-038.03。</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="n">
+        <x:v>46297</x:v>
+      </x:c>
+      <x:c r="G20" s="7" t="str">
+        <x:v>Shipping 最终聊天与 confirmed_fixed_summary 正式三轮</x:v>
+      </x:c>
+      <x:c r="H20" s="16" t="str"/>
+    </x:row>
+    <x:row r="21" ht="92" customHeight="1">
+      <x:c r="A21" s="7" t="str">
+        <x:v>CA-037.02</x:v>
+      </x:c>
+      <x:c r="B21" s="7" t="str">
+        <x:v>Shipping 实测 Markdown 报告交付</x:v>
+      </x:c>
+      <x:c r="C21" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D21" s="7" t="str">
+        <x:v>报告已保存并上传 main，提交 b6445407d74b6e9425d5b21234041d39d922ae3f；包含正式三轮、启动长帧、构建失败及测量限制。上传凭据核对远端提交与正文和两张截图。</x:v>
+      </x:c>
+      <x:c r="E21" s="7" t="str">
+        <x:v>本阶段为测试和方案交付，未实施性能修复；后续按新的实施与验收证据更新。</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="n">
+        <x:v>46297</x:v>
+      </x:c>
+      <x:c r="G21" s="7" t="str">
+        <x:v>最终聊天交付与 git_upload_receipt 远端核对</x:v>
+      </x:c>
+      <x:c r="H21" s="16" t="str"/>
+    </x:row>
+    <x:row r="22" ht="92" customHeight="1">
+      <x:c r="A22" s="7" t="str">
+        <x:v>CA-041</x:v>
+      </x:c>
+      <x:c r="B22" s="7" t="str">
+        <x:v>scene远景组件禁用Nanite</x:v>
+      </x:c>
+      <x:c r="C22" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D22" s="7" t="str">
+        <x:v>按用户要求在实例组件上禁用 Nanite。范围为校园外背景城市、远山岛屿、森林和天际线植被，188 个目标组件全部 disallow_nanite=true；原先仅5个组件启用。</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="str">
+        <x:v>设置阶段已交付；收益与警告复测见 CA-026.02，不从设置变更推断帧率提升。</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G22" s="7" t="str">
+        <x:v>远景修复最终交付与 result 设置回读</x:v>
+      </x:c>
+      <x:c r="H22" s="16" t="str"/>
+    </x:row>
+    <x:row r="23" ht="75" customHeight="1">
+      <x:c r="A23" s="7" t="str">
+        <x:v>CA-041.02</x:v>
+      </x:c>
+      <x:c r="B23" s="7" t="str">
+        <x:v>scene远景投影关闭</x:v>
+      </x:c>
+      <x:c r="C23" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D23" s="7" t="str">
+        <x:v>用户明确选择完全关闭远景阴影。188 个目标组件的投影及接触阴影已关闭，原先投影的140组件、32,598实例停止投影，scene已保存。</x:v>
+      </x:c>
+      <x:c r="E23" s="7" t="str">
+        <x:v>遵循用户最终选择。当前没有同镜头A/B或运行路线证明性能收益，另见 CA-026.02。</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G23" s="7" t="str">
+        <x:v>用户直接选择与 result shadow 回读</x:v>
+      </x:c>
+      <x:c r="H23" s="16" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="1"/>
+      <x:c r="B24" s="1"/>
+      <x:c r="C24" s="1"/>
+      <x:c r="D24" s="1"/>
+      <x:c r="E24" s="1"/>
+      <x:c r="F24" s="1"/>
+      <x:c r="G24" s="1"/>
+      <x:c r="H24" s="1"/>
+    </x:row>
+    <x:row r="25" ht="34" customHeight="1">
+      <x:c r="A25" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B19" s="21" t="str">
+      <x:c r="B25" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C19" s="21"/>
-      <x:c r="D19" s="21"/>
-      <x:c r="E19" s="21"/>
-      <x:c r="F19" s="21"/>
-      <x:c r="G19" s="21"/>
-      <x:c r="H19" s="21"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="1"/>
-      <x:c r="B20" s="1"/>
-      <x:c r="C20" s="1"/>
-      <x:c r="D20" s="1"/>
-      <x:c r="E20" s="1"/>
-      <x:c r="F20" s="1"/>
-      <x:c r="G20" s="1"/>
-      <x:c r="H20" s="1"/>
+      <x:c r="C25" s="21"/>
+      <x:c r="D25" s="21"/>
+      <x:c r="E25" s="21"/>
+      <x:c r="F25" s="21"/>
+      <x:c r="G25" s="21"/>
+      <x:c r="H25" s="21"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="1"/>
+      <x:c r="B26" s="1"/>
+      <x:c r="C26" s="1"/>
+      <x:c r="D26" s="1"/>
+      <x:c r="E26" s="1"/>
+      <x:c r="F26" s="1"/>
+      <x:c r="G26" s="1"/>
+      <x:c r="H26" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B19:H19"/>
+    <x:mergeCell ref="B25:H25"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C17">
+  <x:conditionalFormatting sqref="C8:C23">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -812,13 +956,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C17">
+    <x:dataValidation type="list" sqref="C8:C23">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R758aed5b7dba4b0b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra789c5e4d0934c13"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/性能问题.xlsx
+++ b/ProjectProgress/表格/分类进展/性能问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能问题" sheetId="1" r:id="R3c81e81c57204f12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能问题" sheetId="1" r:id="R9d4a946bb5de456f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress8" displayName="CategoryProgress8" ref="A7:H23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress8" displayName="CategoryProgress8" ref="A7:H25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H25"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-03 09:09:53（北京时间）</x:v>
+        <x:v>更新于 2026-10-04 09:15:53（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,22 +464,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C23,A5)</x:f>
-        <x:v>8</x:v>
+        <x:f>COUNTIF(C8:C25,A5)</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C23,D5)</x:f>
+        <x:f>COUNTIF(C8:C25,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C23,F5)</x:f>
+        <x:f>COUNTIF(C8:C25,F5)</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -544,7 +544,7 @@
       </x:c>
       <x:c r="H8" s="16" t="str"/>
     </x:row>
-    <x:row r="9" ht="126" customHeight="1">
+    <x:row r="9" ht="109" customHeight="1">
       <x:c r="A9" s="7" t="str">
         <x:v>CA-026.03</x:v>
       </x:c>
@@ -555,16 +555,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>已知测试机器 Ryzen 5700X、RTX 4060 Ti、16 GB 系统内存。10 月 2 日 Shipping 诊断包固定视点实测 39.45 应用 FPS，但实际显示帧率和后缓冲像素数未确认。60 FPS 仍为报告假设，用户未指定目标；正常发布构建尚未通过。</x:v>
+        <x:v>测试机器Ryzen5700X/RTX4060Ti/16GB。旧Shipping固定视点39.45应用FPS属于10月2日诊断版本；后续风动GPU增加4.79ms、步态测试约12FPS属编辑器样本。10月3日发布构建已通过，但用户未指定整体帧率、画质及验收路线。</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>确认交付帧率、硬件、画质、内部分辨率和验收路线。实测基准 CA-037 不等于总体达标；发布与像素验收见 CA-038.02、CA-038.03。</x:v>
+        <x:v>确认目标硬件、帧率、画质、像素口径与路线；局部风动A/B或旧诊断成绩不能证明当前单White全场达标。</x:v>
       </x:c>
       <x:c r="F9" s="14" t="n">
-        <x:v>46297</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
-        <x:v>Shipping 报告第 1、4、6 节：测试条件、成绩与目标边界</x:v>
+        <x:v>最新发布、风动样本与版本变化</x:v>
       </x:c>
       <x:c r="H9" s="16" t="str"/>
     </x:row>
@@ -603,16 +603,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
-        <x:v>当前 9,408 组全部 unchanged、0 created，同步仍耗时 135.11 秒，其中 scan 115.061 秒；同次 PIE 总启动 157.99 秒。完整同步钩子已核实，脏组追踪、签名缓存和增量校验尚无实施依据。</x:v>
+        <x:v>旧9,408组无变化ISM同步135.11秒。最新全校园导航工作中9,409组、104,618实例无变化同步135.79秒，scan114.993秒；导航源配置变化978派生批次重建耗141.87秒。仍未找到增量脏组/签名缓存实施或收益验收。</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
-        <x:v>确认是否采用增量同步方案；需分别验证无变化、单组变更、撤销和引用变化。CA-025.02 为已完成的旧内部读取阶段，不能替代本项。</x:v>
+        <x:v>新增导航相关批次同步不等于无变化启动等待优化；若决定处理需分别验收无变化、单组修改、撤销和引用变更。</x:v>
       </x:c>
       <x:c r="F11" s="14" t="n">
-        <x:v>46295</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
-        <x:v>性能排查报告第 3 节：日志与同步钩子</x:v>
+        <x:v>最新导航同步计时与历史诊断</x:v>
       </x:c>
       <x:c r="H11" s="16" t="str"/>
     </x:row>
@@ -906,29 +906,53 @@
       </x:c>
       <x:c r="H23" s="16" t="str"/>
     </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="1"/>
-      <x:c r="B24" s="1"/>
-      <x:c r="C24" s="1"/>
-      <x:c r="D24" s="1"/>
-      <x:c r="E24" s="1"/>
-      <x:c r="F24" s="1"/>
-      <x:c r="G24" s="1"/>
-      <x:c r="H24" s="1"/>
-    </x:row>
-    <x:row r="25" ht="34" customHeight="1">
-      <x:c r="A25" s="3" t="str">
-        <x:v>记录范围</x:v>
-      </x:c>
-      <x:c r="B25" s="21" t="str">
-        <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
-      </x:c>
-      <x:c r="C25" s="21"/>
-      <x:c r="D25" s="21"/>
-      <x:c r="E25" s="21"/>
-      <x:c r="F25" s="21"/>
-      <x:c r="G25" s="21"/>
-      <x:c r="H25" s="21"/>
+    <x:row r="24" ht="92" customHeight="1">
+      <x:c r="A24" s="7" t="str">
+        <x:v>CA-043.04</x:v>
+      </x:c>
+      <x:c r="B24" s="7" t="str">
+        <x:v>植被风动距离衰减与远处停算</x:v>
+      </x:c>
+      <x:c r="C24" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D24" s="7" t="str">
+        <x:v>已用材质GPU顶点偏移和距离衰减，草18米、草花30米、灌木40米、整树120米、棕榈160米后停止。未增加逐株脚本、骨骼、物理或风动纹理采样。</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="str">
+        <x:v>设置交付与实测代价分开判断，实测见CA-043.06。</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G24" s="7" t="str">
+        <x:v>风动性能控制完成说明</x:v>
+      </x:c>
+      <x:c r="H24" s="16" t="str"/>
+    </x:row>
+    <x:row r="25" ht="92" customHeight="1">
+      <x:c r="A25" s="7" t="str">
+        <x:v>CA-043.06</x:v>
+      </x:c>
+      <x:c r="B25" s="7" t="str">
+        <x:v>植被风动同镜头开关性能测量</x:v>
+      </x:c>
+      <x:c r="C25" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D25" s="7" t="str">
+        <x:v>编辑器花坛同镜头，关闭和开启各272帧：GPU中位26.57→31.36ms，总帧62.84→62.98ms，风动GPU增加4.79ms；两组各预热5秒、采样约18秒。</x:v>
+      </x:c>
+      <x:c r="E25" s="7" t="str">
+        <x:v>仅编辑器局部A/B，不是Shipping帧率或总体性能达标。</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G25" s="7" t="str">
+        <x:v>最终风动开关性能样本</x:v>
+      </x:c>
+      <x:c r="H25" s="16" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="1"/>
@@ -940,11 +964,35 @@
       <x:c r="G26" s="1"/>
       <x:c r="H26" s="1"/>
     </x:row>
+    <x:row r="27" ht="34" customHeight="1">
+      <x:c r="A27" s="3" t="str">
+        <x:v>记录范围</x:v>
+      </x:c>
+      <x:c r="B27" s="21" t="str">
+        <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
+      </x:c>
+      <x:c r="C27" s="21"/>
+      <x:c r="D27" s="21"/>
+      <x:c r="E27" s="21"/>
+      <x:c r="F27" s="21"/>
+      <x:c r="G27" s="21"/>
+      <x:c r="H27" s="21"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="1"/>
+      <x:c r="B28" s="1"/>
+      <x:c r="C28" s="1"/>
+      <x:c r="D28" s="1"/>
+      <x:c r="E28" s="1"/>
+      <x:c r="F28" s="1"/>
+      <x:c r="G28" s="1"/>
+      <x:c r="H28" s="1"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B25:H25"/>
+    <x:mergeCell ref="B27:H27"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C23">
+  <x:conditionalFormatting sqref="C8:C25">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -956,13 +1004,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C23">
+    <x:dataValidation type="list" sqref="C8:C25">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra789c5e4d0934c13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85c043bba5eb4fb5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/性能问题.xlsx
+++ b/ProjectProgress/表格/分类进展/性能问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能问题" sheetId="1" r:id="R9d4a946bb5de456f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能问题" sheetId="1" r:id="R8d5e0c5805c047bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress8" displayName="CategoryProgress8" ref="A7:H25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H25"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress8" displayName="CategoryProgress8" ref="A7:H27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H27"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-04 09:15:53（北京时间）</x:v>
+        <x:v>更新于 2026-10-05 09:12:49（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,23 +464,23 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C25,A5)</x:f>
-        <x:v>10</x:v>
+        <x:f>COUNTIF(C8:C27,A5)</x:f>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C25,D5)</x:f>
+        <x:f>COUNTIF(C8:C27,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C25,F5)</x:f>
-        <x:v>8</x:v>
+        <x:f>COUNTIF(C8:C27,F5)</x:f>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
     </x:row>
@@ -544,7 +544,7 @@
       </x:c>
       <x:c r="H8" s="16" t="str"/>
     </x:row>
-    <x:row r="9" ht="109" customHeight="1">
+    <x:row r="9" ht="126" customHeight="1">
       <x:c r="A9" s="7" t="str">
         <x:v>CA-026.03</x:v>
       </x:c>
@@ -555,16 +555,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>测试机器Ryzen5700X/RTX4060Ti/16GB。旧Shipping固定视点39.45应用FPS属于10月2日诊断版本；后续风动GPU增加4.79ms、步态测试约12FPS属编辑器样本。10月3日发布构建已通过，但用户未指定整体帧率、画质及验收路线。</x:v>
+        <x:v>硬件基线Ryzen5700X/RTX4060Ti/16GB，旧诊断39.45应用FPS、新风动与约12FPS编辑器样本均保留。10月5日昼夜预算测试通过但明确未做当前渲染帧耗测量；参考夜景曾预览显存崩溃后恢复。仍未指定整体帧率、画质和验收路线。</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>确认目标硬件、帧率、画质、像素口径与路线；局部风动A/B或旧诊断成绩不能证明当前单White全场达标。</x:v>
+        <x:v>确认当前交付硬件、帧率、画质、像素与路线，最新昼夜局部性能缺口见CA-064.09；不由旧包成绩判断当前达标。</x:v>
       </x:c>
       <x:c r="F9" s="14" t="n">
-        <x:v>46299</x:v>
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
-        <x:v>最新发布、风动样本与版本变化</x:v>
+        <x:v>当前夜景与昼夜测试范围</x:v>
       </x:c>
       <x:c r="H9" s="16" t="str"/>
     </x:row>
@@ -603,16 +603,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
-        <x:v>旧9,408组无变化ISM同步135.11秒。最新全校园导航工作中9,409组、104,618实例无变化同步135.79秒，scan114.993秒；导航源配置变化978派生批次重建耗141.87秒。仍未找到增量脏组/签名缓存实施或收益验收。</x:v>
+        <x:v>旧9408组无变化同步135.11秒；全校园9409组135.79秒保留。最新大纲整理9374组全部复用仍耗141.98秒，scan121.316秒，新增夜景同步147.31秒含创建/替换，不可作为无变化A/B。仍无增量缓存实施证据。</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
-        <x:v>新增导航相关批次同步不等于无变化启动等待优化；若决定处理需分别验收无变化、单组修改、撤销和引用变更。</x:v>
+        <x:v>最新无变化等待仍存在；目录整理和新增灯光同步不证明启动优化完成。</x:v>
       </x:c>
       <x:c r="F11" s="14" t="n">
         <x:v>46299</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
-        <x:v>最新导航同步计时与历史诊断</x:v>
+        <x:v>大纲无变化计时与新增夜景同步边界</x:v>
       </x:c>
       <x:c r="H11" s="16" t="str"/>
     </x:row>
@@ -714,269 +714,293 @@
     </x:row>
     <x:row r="16" ht="109" customHeight="1">
       <x:c r="A16" s="7" t="str">
+        <x:v>CA-064.09</x:v>
+      </x:c>
+      <x:c r="B16" s="7" t="str">
+        <x:v>最新夜景昼夜系统帧耗及显存验收</x:v>
+      </x:c>
+      <x:c r="C16" s="18" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="D16" s="7" t="str">
+        <x:v>错峰预算实现并验证，但final_verified明确rendered_frame_performance_profiled=false；参考夜景预览曾显存崩溃后恢复并限制24fps/85%预览。未找到当前版本同镜头GPU帧耗/显存余量或发布版昼夜路径测试。</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="str">
+        <x:v>若需要性能验收，先确认CA-026.03目标；预算正确不能证明无卡顿或显存余量达标。</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G16" s="7" t="str">
+        <x:v>昼夜明确未测性能与夜景崩溃恢复记录</x:v>
+      </x:c>
+      <x:c r="H16" s="16" t="str"/>
+    </x:row>
+    <x:row r="17" ht="109" customHeight="1">
+      <x:c r="A17" s="7" t="str">
         <x:v>CA-025</x:v>
       </x:c>
-      <x:c r="B16" s="7" t="str">
+      <x:c r="B17" s="7" t="str">
         <x:v>体育馆道路植物 Nanite 配置及短时性能改善</x:v>
       </x:c>
-      <x:c r="C16" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D16" s="7" t="str">
+      <x:c r="C17" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D17" s="7" t="str">
         <x:v>11 类优化网格和 54 个材质/父材质资源用于 9,369 个实例，变换与属性校验通过。
 相同视角 GPU 均值：30.57 → 16.35 ms。
 四组共 1,654 帧无超过 100 ms 的长帧，原始资产保留。</x:v>
       </x:c>
-      <x:c r="E16" s="7" t="str">
+      <x:c r="E17" s="7" t="str">
         <x:v>该阶段完成范围为短时编辑器测试；常态约43–45ms，未证明60FPS、打包版或长时间目标达成。</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="n">
+      <x:c r="F17" s="14" t="n">
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="G16" s="7" t="str">
+      <x:c r="G17" s="7" t="str">
         <x:v>体育馆道路优化实测与完整性记录</x:v>
       </x:c>
-      <x:c r="H16" s="16" t="str"/>
-    </x:row>
-    <x:row r="17" ht="126" customHeight="1">
-      <x:c r="A17" s="7" t="str">
+      <x:c r="H17" s="16" t="str"/>
+    </x:row>
+    <x:row r="18" ht="126" customHeight="1">
+      <x:c r="A18" s="7" t="str">
         <x:v>CA-025.02</x:v>
       </x:c>
-      <x:c r="B17" s="7" t="str">
+      <x:c r="B18" s="7" t="str">
         <x:v>保存和 PIE 同步内部读取优化</x:v>
       </x:c>
-      <x:c r="C17" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D17" s="7" t="str">
+      <x:c r="C18" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D18" s="7" t="str">
         <x:v>9 月 20 日保持全场完整扫描的内部读取优化已交付，实际保存同步由 180.87 降至 145.68 秒，10,264 批次和 110,462 实例保持，引用与语法检查通过。9 月 30 日当前场景无变化同步仍为 135.11 秒；旧阶段交付仍有效，增量同步缺口另见 CA-032.03。</x:v>
       </x:c>
-      <x:c r="E17" s="7" t="str">
+      <x:c r="E18" s="7" t="str">
         <x:v>保留该阶段优化依据。当前无变化同步和启动等待按 CA-032.03 独立跟踪，不能据此宣称整体同步性能达标。</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="n">
+      <x:c r="F18" s="14" t="n">
         <x:v>46295</x:v>
       </x:c>
-      <x:c r="G17" s="7" t="str">
+      <x:c r="G18" s="7" t="str">
         <x:v>历史内部读取优化结果与 scene 当前完整扫描报告</x:v>
       </x:c>
-      <x:c r="H17" s="16" t="str"/>
-    </x:row>
-    <x:row r="18" ht="92" customHeight="1">
-      <x:c r="A18" s="7" t="str">
+      <x:c r="H18" s="16" t="str"/>
+    </x:row>
+    <x:row r="19" ht="92" customHeight="1">
+      <x:c r="A19" s="7" t="str">
         <x:v>CA-026</x:v>
       </x:c>
-      <x:c r="B18" s="7" t="str">
+      <x:c r="B19" s="7" t="str">
         <x:v>固定视角阴影性能基线测量</x:v>
       </x:c>
-      <x:c r="C18" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D18" s="7" t="str">
+      <x:c r="C19" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D19" s="7" t="str">
         <x:v>RTX 4060 Ti 固定编辑器视角开—关—开各 180 帧采样，阴影净 GPU 开销约 2.14 ms/帧、11.8%，显存差约 522 MiB；所有临时设置已恢复。</x:v>
       </x:c>
-      <x:c r="E18" s="7" t="str">
+      <x:c r="E19" s="7" t="str">
         <x:v>把此结果作为固定视角基线；其他视角和实际运行需分别测量。</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="n">
+      <x:c r="F19" s="14" t="n">
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="G18" s="7" t="str">
+      <x:c r="G19" s="7" t="str">
         <x:v>阴影开销实测：有效绘制采样</x:v>
       </x:c>
-      <x:c r="H18" s="16" t="str"/>
-    </x:row>
-    <x:row r="19" ht="126" customHeight="1">
-      <x:c r="A19" s="7" t="str">
+      <x:c r="H19" s="16" t="str"/>
+    </x:row>
+    <x:row r="20" ht="126" customHeight="1">
+      <x:c r="A20" s="7" t="str">
         <x:v>CA-032</x:v>
       </x:c>
-      <x:c r="B19" s="7" t="str">
+      <x:c r="B20" s="7" t="str">
         <x:v>scene 当前性能诊断报告交付</x:v>
       </x:c>
-      <x:c r="C19" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D19" s="7" t="str">
+      <x:c r="C20" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D20" s="7" t="str">
         <x:v>固定编辑器镜头的 340 帧诊断：整帧中位 38.54 ms、主线程 38.47 ms、GPU 13.01 ms，定位 TEDS 等待。10 月 1 日按用户要求转换为 Markdown，结论保留，上传 main 提交 c540e83b047b03ce6476cf720c91eaa6990837b0，替换远端 TXT。</x:v>
       </x:c>
-      <x:c r="E19" s="7" t="str">
+      <x:c r="E20" s="7" t="str">
         <x:v>编辑器诊断报告交付有效。Shipping 独立实测见 CA-037，两个环境镜头与采样口径不同，不能计算优化倍率。</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="n">
+      <x:c r="F20" s="14" t="n">
         <x:v>46296</x:v>
       </x:c>
-      <x:c r="G19" s="7" t="str">
+      <x:c r="G20" s="7" t="str">
         <x:v>性能聊天 Markdown 格式纠正与上传交付</x:v>
       </x:c>
-      <x:c r="H19" s="16" t="str"/>
-    </x:row>
-    <x:row r="20" ht="109" customHeight="1">
-      <x:c r="A20" s="7" t="str">
+      <x:c r="H20" s="16" t="str"/>
+    </x:row>
+    <x:row r="21" ht="109" customHeight="1">
+      <x:c r="A21" s="7" t="str">
         <x:v>CA-037</x:v>
       </x:c>
-      <x:c r="B20" s="7" t="str">
+      <x:c r="B21" s="7" t="str">
         <x:v>Shipping 诊断包固定视点性能基准</x:v>
       </x:c>
-      <x:c r="C20" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D20" s="7" t="str">
+      <x:c r="C21" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D21" s="7" t="str">
         <x:v>教学楼 A 前同一视点三轮各 60 秒、共 7,095 帧：平均应用 39.45 FPS，P95 34.94 ms，1% low 25.90 FPS；最大 48.26 ms，无 &gt;50 ms 帧。视线转向地面的旧约 60 FPS 样本已排除。</x:v>
       </x:c>
-      <x:c r="E20" s="7" t="str">
+      <x:c r="E21" s="7" t="str">
         <x:v>基准阶段已完成，仅代表本机、诊断包与该视点。总体目标见 CA-026.03，标准发布和实际显示验收见 CA-038.02、CA-038.03。</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="n">
-        <x:v>46297</x:v>
-      </x:c>
-      <x:c r="G20" s="7" t="str">
-        <x:v>Shipping 最终聊天与 confirmed_fixed_summary 正式三轮</x:v>
-      </x:c>
-      <x:c r="H20" s="16" t="str"/>
-    </x:row>
-    <x:row r="21" ht="92" customHeight="1">
-      <x:c r="A21" s="7" t="str">
-        <x:v>CA-037.02</x:v>
-      </x:c>
-      <x:c r="B21" s="7" t="str">
-        <x:v>Shipping 实测 Markdown 报告交付</x:v>
-      </x:c>
-      <x:c r="C21" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D21" s="7" t="str">
-        <x:v>报告已保存并上传 main，提交 b6445407d74b6e9425d5b21234041d39d922ae3f；包含正式三轮、启动长帧、构建失败及测量限制。上传凭据核对远端提交与正文和两张截图。</x:v>
-      </x:c>
-      <x:c r="E21" s="7" t="str">
-        <x:v>本阶段为测试和方案交付，未实施性能修复；后续按新的实施与验收证据更新。</x:v>
       </x:c>
       <x:c r="F21" s="14" t="n">
         <x:v>46297</x:v>
       </x:c>
       <x:c r="G21" s="7" t="str">
-        <x:v>最终聊天交付与 git_upload_receipt 远端核对</x:v>
+        <x:v>Shipping 最终聊天与 confirmed_fixed_summary 正式三轮</x:v>
       </x:c>
       <x:c r="H21" s="16" t="str"/>
     </x:row>
     <x:row r="22" ht="92" customHeight="1">
       <x:c r="A22" s="7" t="str">
+        <x:v>CA-037.02</x:v>
+      </x:c>
+      <x:c r="B22" s="7" t="str">
+        <x:v>Shipping 实测 Markdown 报告交付</x:v>
+      </x:c>
+      <x:c r="C22" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D22" s="7" t="str">
+        <x:v>报告已保存并上传 main，提交 b6445407d74b6e9425d5b21234041d39d922ae3f；包含正式三轮、启动长帧、构建失败及测量限制。上传凭据核对远端提交与正文和两张截图。</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="str">
+        <x:v>本阶段为测试和方案交付，未实施性能修复；后续按新的实施与验收证据更新。</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="n">
+        <x:v>46297</x:v>
+      </x:c>
+      <x:c r="G22" s="7" t="str">
+        <x:v>最终聊天交付与 git_upload_receipt 远端核对</x:v>
+      </x:c>
+      <x:c r="H22" s="16" t="str"/>
+    </x:row>
+    <x:row r="23" ht="92" customHeight="1">
+      <x:c r="A23" s="7" t="str">
         <x:v>CA-041</x:v>
       </x:c>
-      <x:c r="B22" s="7" t="str">
+      <x:c r="B23" s="7" t="str">
         <x:v>scene远景组件禁用Nanite</x:v>
       </x:c>
-      <x:c r="C22" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D22" s="7" t="str">
+      <x:c r="C23" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D23" s="7" t="str">
         <x:v>按用户要求在实例组件上禁用 Nanite。范围为校园外背景城市、远山岛屿、森林和天际线植被，188 个目标组件全部 disallow_nanite=true；原先仅5个组件启用。</x:v>
       </x:c>
-      <x:c r="E22" s="7" t="str">
+      <x:c r="E23" s="7" t="str">
         <x:v>设置阶段已交付；收益与警告复测见 CA-026.02，不从设置变更推断帧率提升。</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="G22" s="7" t="str">
-        <x:v>远景修复最终交付与 result 设置回读</x:v>
-      </x:c>
-      <x:c r="H22" s="16" t="str"/>
-    </x:row>
-    <x:row r="23" ht="75" customHeight="1">
-      <x:c r="A23" s="7" t="str">
-        <x:v>CA-041.02</x:v>
-      </x:c>
-      <x:c r="B23" s="7" t="str">
-        <x:v>scene远景投影关闭</x:v>
-      </x:c>
-      <x:c r="C23" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D23" s="7" t="str">
-        <x:v>用户明确选择完全关闭远景阴影。188 个目标组件的投影及接触阴影已关闭，原先投影的140组件、32,598实例停止投影，scene已保存。</x:v>
-      </x:c>
-      <x:c r="E23" s="7" t="str">
-        <x:v>遵循用户最终选择。当前没有同镜头A/B或运行路线证明性能收益，另见 CA-026.02。</x:v>
       </x:c>
       <x:c r="F23" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G23" s="7" t="str">
-        <x:v>用户直接选择与 result shadow 回读</x:v>
+        <x:v>远景修复最终交付与 result 设置回读</x:v>
       </x:c>
       <x:c r="H23" s="16" t="str"/>
     </x:row>
-    <x:row r="24" ht="92" customHeight="1">
+    <x:row r="24" ht="75" customHeight="1">
       <x:c r="A24" s="7" t="str">
-        <x:v>CA-043.04</x:v>
+        <x:v>CA-041.02</x:v>
       </x:c>
       <x:c r="B24" s="7" t="str">
-        <x:v>植被风动距离衰减与远处停算</x:v>
+        <x:v>scene远景投影关闭</x:v>
       </x:c>
       <x:c r="C24" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D24" s="7" t="str">
-        <x:v>已用材质GPU顶点偏移和距离衰减，草18米、草花30米、灌木40米、整树120米、棕榈160米后停止。未增加逐株脚本、骨骼、物理或风动纹理采样。</x:v>
+        <x:v>用户明确选择完全关闭远景阴影。188 个目标组件的投影及接触阴影已关闭，原先投影的140组件、32,598实例停止投影，scene已保存。</x:v>
       </x:c>
       <x:c r="E24" s="7" t="str">
-        <x:v>设置交付与实测代价分开判断，实测见CA-043.06。</x:v>
+        <x:v>遵循用户最终选择。当前没有同镜头A/B或运行路线证明性能收益，另见 CA-026.02。</x:v>
       </x:c>
       <x:c r="F24" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G24" s="7" t="str">
-        <x:v>风动性能控制完成说明</x:v>
+        <x:v>用户直接选择与 result shadow 回读</x:v>
       </x:c>
       <x:c r="H24" s="16" t="str"/>
     </x:row>
     <x:row r="25" ht="92" customHeight="1">
       <x:c r="A25" s="7" t="str">
-        <x:v>CA-043.06</x:v>
+        <x:v>CA-043.04</x:v>
       </x:c>
       <x:c r="B25" s="7" t="str">
-        <x:v>植被风动同镜头开关性能测量</x:v>
+        <x:v>植被风动距离衰减与远处停算</x:v>
       </x:c>
       <x:c r="C25" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D25" s="7" t="str">
-        <x:v>编辑器花坛同镜头，关闭和开启各272帧：GPU中位26.57→31.36ms，总帧62.84→62.98ms，风动GPU增加4.79ms；两组各预热5秒、采样约18秒。</x:v>
+        <x:v>已用材质GPU顶点偏移和距离衰减，草18米、草花30米、灌木40米、整树120米、棕榈160米后停止。未增加逐株脚本、骨骼、物理或风动纹理采样。</x:v>
       </x:c>
       <x:c r="E25" s="7" t="str">
-        <x:v>仅编辑器局部A/B，不是Shipping帧率或总体性能达标。</x:v>
+        <x:v>设置交付与实测代价分开判断，实测见CA-043.06。</x:v>
       </x:c>
       <x:c r="F25" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G25" s="7" t="str">
+        <x:v>风动性能控制完成说明</x:v>
+      </x:c>
+      <x:c r="H25" s="16" t="str"/>
+    </x:row>
+    <x:row r="26" ht="92" customHeight="1">
+      <x:c r="A26" s="7" t="str">
+        <x:v>CA-043.06</x:v>
+      </x:c>
+      <x:c r="B26" s="7" t="str">
+        <x:v>植被风动同镜头开关性能测量</x:v>
+      </x:c>
+      <x:c r="C26" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D26" s="7" t="str">
+        <x:v>编辑器花坛同镜头，关闭和开启各272帧：GPU中位26.57→31.36ms，总帧62.84→62.98ms，风动GPU增加4.79ms；两组各预热5秒、采样约18秒。</x:v>
+      </x:c>
+      <x:c r="E26" s="7" t="str">
+        <x:v>仅编辑器局部A/B，不是Shipping帧率或总体性能达标。</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G26" s="7" t="str">
         <x:v>最终风动开关性能样本</x:v>
       </x:c>
-      <x:c r="H25" s="16" t="str"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="1"/>
-      <x:c r="B26" s="1"/>
-      <x:c r="C26" s="1"/>
-      <x:c r="D26" s="1"/>
-      <x:c r="E26" s="1"/>
-      <x:c r="F26" s="1"/>
-      <x:c r="G26" s="1"/>
-      <x:c r="H26" s="1"/>
-    </x:row>
-    <x:row r="27" ht="34" customHeight="1">
-      <x:c r="A27" s="3" t="str">
-        <x:v>记录范围</x:v>
-      </x:c>
-      <x:c r="B27" s="21" t="str">
-        <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
-      </x:c>
-      <x:c r="C27" s="21"/>
-      <x:c r="D27" s="21"/>
-      <x:c r="E27" s="21"/>
-      <x:c r="F27" s="21"/>
-      <x:c r="G27" s="21"/>
-      <x:c r="H27" s="21"/>
+      <x:c r="H26" s="16" t="str"/>
+    </x:row>
+    <x:row r="27" ht="92" customHeight="1">
+      <x:c r="A27" s="7" t="str">
+        <x:v>CA-064.04</x:v>
+      </x:c>
+      <x:c r="B27" s="7" t="str">
+        <x:v>昼夜分批开灯与更新预算实现</x:v>
+      </x:c>
+      <x:c r="C27" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D27" s="7" t="str">
+        <x:v>每帧最多新开4灯，其中投影灯最多1，常规更新16灯，夜启动约30秒错峰且默认6秒渐亮。初版1044帧观测峰值开4/更新16通过；白天关灯不受更新上限。</x:v>
+      </x:c>
+      <x:c r="E27" s="7" t="str">
+        <x:v>已验预算和渐变逻辑，不等同整帧性能达标，见CA-064.09。</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G27" s="7" t="str">
+        <x:v>runtime_verified与最新修订说明</x:v>
+      </x:c>
+      <x:c r="H27" s="16" t="str"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="1"/>
@@ -988,11 +1012,35 @@
       <x:c r="G28" s="1"/>
       <x:c r="H28" s="1"/>
     </x:row>
+    <x:row r="29" ht="34" customHeight="1">
+      <x:c r="A29" s="3" t="str">
+        <x:v>记录范围</x:v>
+      </x:c>
+      <x:c r="B29" s="21" t="str">
+        <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
+      </x:c>
+      <x:c r="C29" s="21"/>
+      <x:c r="D29" s="21"/>
+      <x:c r="E29" s="21"/>
+      <x:c r="F29" s="21"/>
+      <x:c r="G29" s="21"/>
+      <x:c r="H29" s="21"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="1"/>
+      <x:c r="B30" s="1"/>
+      <x:c r="C30" s="1"/>
+      <x:c r="D30" s="1"/>
+      <x:c r="E30" s="1"/>
+      <x:c r="F30" s="1"/>
+      <x:c r="G30" s="1"/>
+      <x:c r="H30" s="1"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B27:H27"/>
+    <x:mergeCell ref="B29:H29"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C25">
+  <x:conditionalFormatting sqref="C8:C27">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -1004,13 +1052,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C25">
+    <x:dataValidation type="list" sqref="C8:C27">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85c043bba5eb4fb5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68ab155a9f634975"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/性能问题.xlsx
+++ b/ProjectProgress/表格/分类进展/性能问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能问题" sheetId="1" r:id="R8d5e0c5805c047bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能问题" sheetId="1" r:id="R14cae77f2f5d42eb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress8" displayName="CategoryProgress8" ref="A7:H27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H27"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress8" displayName="CategoryProgress8" ref="A7:H30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H30"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-05 09:12:49（北京时间）</x:v>
+        <x:v>更新于 2026-10-06 09:08:50（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,23 +464,23 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C27,A5)</x:f>
-        <x:v>11</x:v>
+        <x:f>COUNTIF(C8:C30,A5)</x:f>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C27,D5)</x:f>
+        <x:f>COUNTIF(C8:C30,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C27,F5)</x:f>
-        <x:v>9</x:v>
+        <x:f>COUNTIF(C8:C30,F5)</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
     </x:row>
@@ -555,10 +555,10 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>硬件基线Ryzen5700X/RTX4060Ti/16GB，旧诊断39.45应用FPS、新风动与约12FPS编辑器样本均保留。10月5日昼夜预算测试通过但明确未做当前渲染帧耗测量；参考夜景曾预览显存崩溃后恢复。仍未指定整体帧率、画质和验收路线。</x:v>
+        <x:v>硬件与旧Shipping39.45应用FPS基线保留。教学楼材质两固定编辑器视角GPU中位变化约1%以内已验；之后新草地42.4万实例无对应帧耗实测。最新月亮/扫射低开销预览恢复不能证明全校园目标达标，仍无完整硬件、画质、像素和路线标准。</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>确认当前交付硬件、帧率、画质、像素与路线，最新昼夜局部性能缺口见CA-064.09；不由旧包成绩判断当前达标。</x:v>
+        <x:v>目标待确认；局部材质实测见CA-070.05，草地实际影响见CA-071.06，完整昼夜见CA-064.09。</x:v>
       </x:c>
       <x:c r="F9" s="14" t="n">
         <x:v>46300</x:v>
@@ -723,10 +723,10 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D16" s="7" t="str">
-        <x:v>错峰预算实现并验证，但final_verified明确rendered_frame_performance_profiled=false；参考夜景预览曾显存崩溃后恢复并限制24fps/85%预览。未找到当前版本同镜头GPU帧耗/显存余量或发布版昼夜路径测试。</x:v>
+        <x:v>旧错峰预算通过但未测渲染帧耗。新月亮高分辨率截图曾耗尽虚拟内存，扫射预览亦显存不足后恢复；测试使用临时低开销预览设置。教学楼材质仅两固定日间视角A/B通过，不能代替完整夜景、昼夜路径和显存余量验收。</x:v>
       </x:c>
       <x:c r="E16" s="7" t="str">
-        <x:v>若需要性能验收，先确认CA-026.03目标；预算正确不能证明无卡顿或显存余量达标。</x:v>
+        <x:v>整体目标仍见CA-026.03；材质局部实测见CA-070.05，草地实测缺口见CA-071.06。</x:v>
       </x:c>
       <x:c r="F16" s="14" t="n">
         <x:v>46300</x:v>
@@ -736,311 +736,383 @@
       </x:c>
       <x:c r="H16" s="16" t="str"/>
     </x:row>
-    <x:row r="17" ht="109" customHeight="1">
+    <x:row r="17" ht="92" customHeight="1">
       <x:c r="A17" s="7" t="str">
+        <x:v>CA-071.06</x:v>
+      </x:c>
+      <x:c r="B17" s="7" t="str">
+        <x:v>密铺草地实际GPU帧耗与显存影响</x:v>
+      </x:c>
+      <x:c r="C17" s="18" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="D17" s="7" t="str">
+        <x:v>用户要求注意性能；现有证据只验证分块、LOD和剔除设置，未找到草地前后同视角GPU帧耗、显存余量或Shipping路径实测。教学楼材质数据早于草地交付。</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="str">
+        <x:v>若需要判定性能影响，核对草地对应实测及CA-026.03目标；不自行运行性能测试。</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G17" s="7" t="str">
+        <x:v>草地检查范围与局部材质实测时序</x:v>
+      </x:c>
+      <x:c r="H17" s="16" t="str"/>
+    </x:row>
+    <x:row r="18" ht="109" customHeight="1">
+      <x:c r="A18" s="7" t="str">
         <x:v>CA-025</x:v>
       </x:c>
-      <x:c r="B17" s="7" t="str">
+      <x:c r="B18" s="7" t="str">
         <x:v>体育馆道路植物 Nanite 配置及短时性能改善</x:v>
       </x:c>
-      <x:c r="C17" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D17" s="7" t="str">
+      <x:c r="C18" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D18" s="7" t="str">
         <x:v>11 类优化网格和 54 个材质/父材质资源用于 9,369 个实例，变换与属性校验通过。
 相同视角 GPU 均值：30.57 → 16.35 ms。
 四组共 1,654 帧无超过 100 ms 的长帧，原始资产保留。</x:v>
       </x:c>
-      <x:c r="E17" s="7" t="str">
+      <x:c r="E18" s="7" t="str">
         <x:v>该阶段完成范围为短时编辑器测试；常态约43–45ms，未证明60FPS、打包版或长时间目标达成。</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="n">
+      <x:c r="F18" s="14" t="n">
         <x:v>46285</x:v>
       </x:c>
-      <x:c r="G17" s="7" t="str">
+      <x:c r="G18" s="7" t="str">
         <x:v>体育馆道路优化实测与完整性记录</x:v>
       </x:c>
-      <x:c r="H17" s="16" t="str"/>
-    </x:row>
-    <x:row r="18" ht="126" customHeight="1">
-      <x:c r="A18" s="7" t="str">
+      <x:c r="H18" s="16" t="str"/>
+    </x:row>
+    <x:row r="19" ht="126" customHeight="1">
+      <x:c r="A19" s="7" t="str">
         <x:v>CA-025.02</x:v>
       </x:c>
-      <x:c r="B18" s="7" t="str">
+      <x:c r="B19" s="7" t="str">
         <x:v>保存和 PIE 同步内部读取优化</x:v>
       </x:c>
-      <x:c r="C18" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D18" s="7" t="str">
+      <x:c r="C19" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D19" s="7" t="str">
         <x:v>9 月 20 日保持全场完整扫描的内部读取优化已交付，实际保存同步由 180.87 降至 145.68 秒，10,264 批次和 110,462 实例保持，引用与语法检查通过。9 月 30 日当前场景无变化同步仍为 135.11 秒；旧阶段交付仍有效，增量同步缺口另见 CA-032.03。</x:v>
       </x:c>
-      <x:c r="E18" s="7" t="str">
+      <x:c r="E19" s="7" t="str">
         <x:v>保留该阶段优化依据。当前无变化同步和启动等待按 CA-032.03 独立跟踪，不能据此宣称整体同步性能达标。</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="n">
+      <x:c r="F19" s="14" t="n">
         <x:v>46295</x:v>
       </x:c>
-      <x:c r="G18" s="7" t="str">
+      <x:c r="G19" s="7" t="str">
         <x:v>历史内部读取优化结果与 scene 当前完整扫描报告</x:v>
       </x:c>
-      <x:c r="H18" s="16" t="str"/>
-    </x:row>
-    <x:row r="19" ht="92" customHeight="1">
-      <x:c r="A19" s="7" t="str">
+      <x:c r="H19" s="16" t="str"/>
+    </x:row>
+    <x:row r="20" ht="92" customHeight="1">
+      <x:c r="A20" s="7" t="str">
         <x:v>CA-026</x:v>
       </x:c>
-      <x:c r="B19" s="7" t="str">
+      <x:c r="B20" s="7" t="str">
         <x:v>固定视角阴影性能基线测量</x:v>
       </x:c>
-      <x:c r="C19" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D19" s="7" t="str">
+      <x:c r="C20" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D20" s="7" t="str">
         <x:v>RTX 4060 Ti 固定编辑器视角开—关—开各 180 帧采样，阴影净 GPU 开销约 2.14 ms/帧、11.8%，显存差约 522 MiB；所有临时设置已恢复。</x:v>
       </x:c>
-      <x:c r="E19" s="7" t="str">
+      <x:c r="E20" s="7" t="str">
         <x:v>把此结果作为固定视角基线；其他视角和实际运行需分别测量。</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="n">
+      <x:c r="F20" s="14" t="n">
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="G19" s="7" t="str">
+      <x:c r="G20" s="7" t="str">
         <x:v>阴影开销实测：有效绘制采样</x:v>
       </x:c>
-      <x:c r="H19" s="16" t="str"/>
-    </x:row>
-    <x:row r="20" ht="126" customHeight="1">
-      <x:c r="A20" s="7" t="str">
+      <x:c r="H20" s="16" t="str"/>
+    </x:row>
+    <x:row r="21" ht="126" customHeight="1">
+      <x:c r="A21" s="7" t="str">
         <x:v>CA-032</x:v>
       </x:c>
-      <x:c r="B20" s="7" t="str">
+      <x:c r="B21" s="7" t="str">
         <x:v>scene 当前性能诊断报告交付</x:v>
       </x:c>
-      <x:c r="C20" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D20" s="7" t="str">
+      <x:c r="C21" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D21" s="7" t="str">
         <x:v>固定编辑器镜头的 340 帧诊断：整帧中位 38.54 ms、主线程 38.47 ms、GPU 13.01 ms，定位 TEDS 等待。10 月 1 日按用户要求转换为 Markdown，结论保留，上传 main 提交 c540e83b047b03ce6476cf720c91eaa6990837b0，替换远端 TXT。</x:v>
       </x:c>
-      <x:c r="E20" s="7" t="str">
+      <x:c r="E21" s="7" t="str">
         <x:v>编辑器诊断报告交付有效。Shipping 独立实测见 CA-037，两个环境镜头与采样口径不同，不能计算优化倍率。</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="n">
+      <x:c r="F21" s="14" t="n">
         <x:v>46296</x:v>
       </x:c>
-      <x:c r="G20" s="7" t="str">
+      <x:c r="G21" s="7" t="str">
         <x:v>性能聊天 Markdown 格式纠正与上传交付</x:v>
       </x:c>
-      <x:c r="H20" s="16" t="str"/>
-    </x:row>
-    <x:row r="21" ht="109" customHeight="1">
-      <x:c r="A21" s="7" t="str">
+      <x:c r="H21" s="16" t="str"/>
+    </x:row>
+    <x:row r="22" ht="109" customHeight="1">
+      <x:c r="A22" s="7" t="str">
         <x:v>CA-037</x:v>
       </x:c>
-      <x:c r="B21" s="7" t="str">
+      <x:c r="B22" s="7" t="str">
         <x:v>Shipping 诊断包固定视点性能基准</x:v>
       </x:c>
-      <x:c r="C21" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D21" s="7" t="str">
+      <x:c r="C22" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D22" s="7" t="str">
         <x:v>教学楼 A 前同一视点三轮各 60 秒、共 7,095 帧：平均应用 39.45 FPS，P95 34.94 ms，1% low 25.90 FPS；最大 48.26 ms，无 &gt;50 ms 帧。视线转向地面的旧约 60 FPS 样本已排除。</x:v>
       </x:c>
-      <x:c r="E21" s="7" t="str">
+      <x:c r="E22" s="7" t="str">
         <x:v>基准阶段已完成，仅代表本机、诊断包与该视点。总体目标见 CA-026.03，标准发布和实际显示验收见 CA-038.02、CA-038.03。</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="n">
-        <x:v>46297</x:v>
-      </x:c>
-      <x:c r="G21" s="7" t="str">
-        <x:v>Shipping 最终聊天与 confirmed_fixed_summary 正式三轮</x:v>
-      </x:c>
-      <x:c r="H21" s="16" t="str"/>
-    </x:row>
-    <x:row r="22" ht="92" customHeight="1">
-      <x:c r="A22" s="7" t="str">
-        <x:v>CA-037.02</x:v>
-      </x:c>
-      <x:c r="B22" s="7" t="str">
-        <x:v>Shipping 实测 Markdown 报告交付</x:v>
-      </x:c>
-      <x:c r="C22" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D22" s="7" t="str">
-        <x:v>报告已保存并上传 main，提交 b6445407d74b6e9425d5b21234041d39d922ae3f；包含正式三轮、启动长帧、构建失败及测量限制。上传凭据核对远端提交与正文和两张截图。</x:v>
-      </x:c>
-      <x:c r="E22" s="7" t="str">
-        <x:v>本阶段为测试和方案交付，未实施性能修复；后续按新的实施与验收证据更新。</x:v>
       </x:c>
       <x:c r="F22" s="14" t="n">
         <x:v>46297</x:v>
       </x:c>
       <x:c r="G22" s="7" t="str">
-        <x:v>最终聊天交付与 git_upload_receipt 远端核对</x:v>
+        <x:v>Shipping 最终聊天与 confirmed_fixed_summary 正式三轮</x:v>
       </x:c>
       <x:c r="H22" s="16" t="str"/>
     </x:row>
     <x:row r="23" ht="92" customHeight="1">
       <x:c r="A23" s="7" t="str">
+        <x:v>CA-037.02</x:v>
+      </x:c>
+      <x:c r="B23" s="7" t="str">
+        <x:v>Shipping 实测 Markdown 报告交付</x:v>
+      </x:c>
+      <x:c r="C23" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D23" s="7" t="str">
+        <x:v>报告已保存并上传 main，提交 b6445407d74b6e9425d5b21234041d39d922ae3f；包含正式三轮、启动长帧、构建失败及测量限制。上传凭据核对远端提交与正文和两张截图。</x:v>
+      </x:c>
+      <x:c r="E23" s="7" t="str">
+        <x:v>本阶段为测试和方案交付，未实施性能修复；后续按新的实施与验收证据更新。</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="n">
+        <x:v>46297</x:v>
+      </x:c>
+      <x:c r="G23" s="7" t="str">
+        <x:v>最终聊天交付与 git_upload_receipt 远端核对</x:v>
+      </x:c>
+      <x:c r="H23" s="16" t="str"/>
+    </x:row>
+    <x:row r="24" ht="92" customHeight="1">
+      <x:c r="A24" s="7" t="str">
         <x:v>CA-041</x:v>
       </x:c>
-      <x:c r="B23" s="7" t="str">
+      <x:c r="B24" s="7" t="str">
         <x:v>scene远景组件禁用Nanite</x:v>
       </x:c>
-      <x:c r="C23" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D23" s="7" t="str">
+      <x:c r="C24" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D24" s="7" t="str">
         <x:v>按用户要求在实例组件上禁用 Nanite。范围为校园外背景城市、远山岛屿、森林和天际线植被，188 个目标组件全部 disallow_nanite=true；原先仅5个组件启用。</x:v>
       </x:c>
-      <x:c r="E23" s="7" t="str">
+      <x:c r="E24" s="7" t="str">
         <x:v>设置阶段已交付；收益与警告复测见 CA-026.02，不从设置变更推断帧率提升。</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="n">
-        <x:v>46298</x:v>
-      </x:c>
-      <x:c r="G23" s="7" t="str">
-        <x:v>远景修复最终交付与 result 设置回读</x:v>
-      </x:c>
-      <x:c r="H23" s="16" t="str"/>
-    </x:row>
-    <x:row r="24" ht="75" customHeight="1">
-      <x:c r="A24" s="7" t="str">
-        <x:v>CA-041.02</x:v>
-      </x:c>
-      <x:c r="B24" s="7" t="str">
-        <x:v>scene远景投影关闭</x:v>
-      </x:c>
-      <x:c r="C24" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D24" s="7" t="str">
-        <x:v>用户明确选择完全关闭远景阴影。188 个目标组件的投影及接触阴影已关闭，原先投影的140组件、32,598实例停止投影，scene已保存。</x:v>
-      </x:c>
-      <x:c r="E24" s="7" t="str">
-        <x:v>遵循用户最终选择。当前没有同镜头A/B或运行路线证明性能收益，另见 CA-026.02。</x:v>
       </x:c>
       <x:c r="F24" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G24" s="7" t="str">
-        <x:v>用户直接选择与 result shadow 回读</x:v>
+        <x:v>远景修复最终交付与 result 设置回读</x:v>
       </x:c>
       <x:c r="H24" s="16" t="str"/>
     </x:row>
-    <x:row r="25" ht="92" customHeight="1">
+    <x:row r="25" ht="75" customHeight="1">
       <x:c r="A25" s="7" t="str">
-        <x:v>CA-043.04</x:v>
+        <x:v>CA-041.02</x:v>
       </x:c>
       <x:c r="B25" s="7" t="str">
-        <x:v>植被风动距离衰减与远处停算</x:v>
+        <x:v>scene远景投影关闭</x:v>
       </x:c>
       <x:c r="C25" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D25" s="7" t="str">
-        <x:v>已用材质GPU顶点偏移和距离衰减，草18米、草花30米、灌木40米、整树120米、棕榈160米后停止。未增加逐株脚本、骨骼、物理或风动纹理采样。</x:v>
+        <x:v>用户明确选择完全关闭远景阴影。188 个目标组件的投影及接触阴影已关闭，原先投影的140组件、32,598实例停止投影，scene已保存。</x:v>
       </x:c>
       <x:c r="E25" s="7" t="str">
-        <x:v>设置交付与实测代价分开判断，实测见CA-043.06。</x:v>
+        <x:v>遵循用户最终选择。当前没有同镜头A/B或运行路线证明性能收益，另见 CA-026.02。</x:v>
       </x:c>
       <x:c r="F25" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G25" s="7" t="str">
-        <x:v>风动性能控制完成说明</x:v>
+        <x:v>用户直接选择与 result shadow 回读</x:v>
       </x:c>
       <x:c r="H25" s="16" t="str"/>
     </x:row>
     <x:row r="26" ht="92" customHeight="1">
       <x:c r="A26" s="7" t="str">
-        <x:v>CA-043.06</x:v>
+        <x:v>CA-043.04</x:v>
       </x:c>
       <x:c r="B26" s="7" t="str">
-        <x:v>植被风动同镜头开关性能测量</x:v>
+        <x:v>植被风动距离衰减与远处停算</x:v>
       </x:c>
       <x:c r="C26" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D26" s="7" t="str">
-        <x:v>编辑器花坛同镜头，关闭和开启各272帧：GPU中位26.57→31.36ms，总帧62.84→62.98ms，风动GPU增加4.79ms；两组各预热5秒、采样约18秒。</x:v>
+        <x:v>已用材质GPU顶点偏移和距离衰减，草18米、草花30米、灌木40米、整树120米、棕榈160米后停止。未增加逐株脚本、骨骼、物理或风动纹理采样。</x:v>
       </x:c>
       <x:c r="E26" s="7" t="str">
-        <x:v>仅编辑器局部A/B，不是Shipping帧率或总体性能达标。</x:v>
+        <x:v>设置交付与实测代价分开判断，实测见CA-043.06。</x:v>
       </x:c>
       <x:c r="F26" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
       <x:c r="G26" s="7" t="str">
-        <x:v>最终风动开关性能样本</x:v>
+        <x:v>风动性能控制完成说明</x:v>
       </x:c>
       <x:c r="H26" s="16" t="str"/>
     </x:row>
     <x:row r="27" ht="92" customHeight="1">
       <x:c r="A27" s="7" t="str">
+        <x:v>CA-043.06</x:v>
+      </x:c>
+      <x:c r="B27" s="7" t="str">
+        <x:v>植被风动同镜头开关性能测量</x:v>
+      </x:c>
+      <x:c r="C27" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D27" s="7" t="str">
+        <x:v>编辑器花坛同镜头，关闭和开启各272帧：GPU中位26.57→31.36ms，总帧62.84→62.98ms，风动GPU增加4.79ms；两组各预热5秒、采样约18秒。</x:v>
+      </x:c>
+      <x:c r="E27" s="7" t="str">
+        <x:v>仅编辑器局部A/B，不是Shipping帧率或总体性能达标。</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G27" s="7" t="str">
+        <x:v>最终风动开关性能样本</x:v>
+      </x:c>
+      <x:c r="H27" s="16" t="str"/>
+    </x:row>
+    <x:row r="28" ht="92" customHeight="1">
+      <x:c r="A28" s="7" t="str">
         <x:v>CA-064.04</x:v>
       </x:c>
-      <x:c r="B27" s="7" t="str">
+      <x:c r="B28" s="7" t="str">
         <x:v>昼夜分批开灯与更新预算实现</x:v>
       </x:c>
-      <x:c r="C27" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D27" s="7" t="str">
-        <x:v>每帧最多新开4灯，其中投影灯最多1，常规更新16灯，夜启动约30秒错峰且默认6秒渐亮。初版1044帧观测峰值开4/更新16通过；白天关灯不受更新上限。</x:v>
-      </x:c>
-      <x:c r="E27" s="7" t="str">
-        <x:v>已验预算和渐变逻辑，不等同整帧性能达标，见CA-064.09。</x:v>
-      </x:c>
-      <x:c r="F27" s="14" t="n">
+      <x:c r="C28" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D28" s="7" t="str">
+        <x:v>保留每帧最多新开4灯（投影灯最多1）、更新16灯预算。默认单灯渐变由6秒放慢至12秒，17:00–19:15错峰窗口约56秒；最新预算及过渡回归通过。</x:v>
+      </x:c>
+      <x:c r="E28" s="7" t="str">
+        <x:v>实现预算已验，不等同整帧性能达标，见CA-064.09。</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="n">
         <x:v>46300</x:v>
       </x:c>
-      <x:c r="G27" s="7" t="str">
+      <x:c r="G28" s="7" t="str">
         <x:v>runtime_verified与最新修订说明</x:v>
       </x:c>
-      <x:c r="H27" s="16" t="str"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="1"/>
-      <x:c r="B28" s="1"/>
-      <x:c r="C28" s="1"/>
-      <x:c r="D28" s="1"/>
-      <x:c r="E28" s="1"/>
-      <x:c r="F28" s="1"/>
-      <x:c r="G28" s="1"/>
-      <x:c r="H28" s="1"/>
-    </x:row>
-    <x:row r="29" ht="34" customHeight="1">
-      <x:c r="A29" s="3" t="str">
+      <x:c r="H28" s="16" t="str"/>
+    </x:row>
+    <x:row r="29" ht="109" customHeight="1">
+      <x:c r="A29" s="7" t="str">
+        <x:v>CA-070.05</x:v>
+      </x:c>
+      <x:c r="B29" s="7" t="str">
+        <x:v>教学楼材质固定视角GPU对比</x:v>
+      </x:c>
+      <x:c r="C29" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D29" s="7" t="str">
+        <x:v>RTX4060Ti编辑器10:30同分辨率，两视角前后各360帧：GPU中位A28.0353→28.0703ms（+0.12%）、B38.5722→38.2128ms（-0.93%）；P95分别32.5221→32.7808、41.3584→41.8701ms。</x:v>
+      </x:c>
+      <x:c r="E29" s="7" t="str">
+        <x:v>本项完成局部材质A/B；未代表之后纯色门、草地、所有昼夜或Shipping总体目标。</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G29" s="7" t="str">
+        <x:v>材质前后360帧原始数据与限制说明</x:v>
+      </x:c>
+      <x:c r="H29" s="16" t="str"/>
+    </x:row>
+    <x:row r="30" ht="75" customHeight="1">
+      <x:c r="A30" s="7" t="str">
+        <x:v>CA-071.04</x:v>
+      </x:c>
+      <x:c r="B30" s="7" t="str">
+        <x:v>密铺草地分块LOD与距离剔除设置</x:v>
+      </x:c>
+      <x:c r="C30" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D30" s="7" t="str">
+        <x:v>246块约25m范围实例化，三档LOD，35m开始渐隐48m剔除；关闭碰撞导航、动态投影和草地光追可见性，设置验证通过。</x:v>
+      </x:c>
+      <x:c r="E30" s="7" t="str">
+        <x:v>完成的是控制开销设置，实际帧耗尚未量测见CA-071.06。</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G30" s="7" t="str">
+        <x:v>草地布局策略与设置回读</x:v>
+      </x:c>
+      <x:c r="H30" s="16" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="1"/>
+      <x:c r="B31" s="1"/>
+      <x:c r="C31" s="1"/>
+      <x:c r="D31" s="1"/>
+      <x:c r="E31" s="1"/>
+      <x:c r="F31" s="1"/>
+      <x:c r="G31" s="1"/>
+      <x:c r="H31" s="1"/>
+    </x:row>
+    <x:row r="32" ht="34" customHeight="1">
+      <x:c r="A32" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B29" s="21" t="str">
+      <x:c r="B32" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C29" s="21"/>
-      <x:c r="D29" s="21"/>
-      <x:c r="E29" s="21"/>
-      <x:c r="F29" s="21"/>
-      <x:c r="G29" s="21"/>
-      <x:c r="H29" s="21"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="1"/>
-      <x:c r="B30" s="1"/>
-      <x:c r="C30" s="1"/>
-      <x:c r="D30" s="1"/>
-      <x:c r="E30" s="1"/>
-      <x:c r="F30" s="1"/>
-      <x:c r="G30" s="1"/>
-      <x:c r="H30" s="1"/>
+      <x:c r="C32" s="21"/>
+      <x:c r="D32" s="21"/>
+      <x:c r="E32" s="21"/>
+      <x:c r="F32" s="21"/>
+      <x:c r="G32" s="21"/>
+      <x:c r="H32" s="21"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="1"/>
+      <x:c r="B33" s="1"/>
+      <x:c r="C33" s="1"/>
+      <x:c r="D33" s="1"/>
+      <x:c r="E33" s="1"/>
+      <x:c r="F33" s="1"/>
+      <x:c r="G33" s="1"/>
+      <x:c r="H33" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B29:H29"/>
+    <x:mergeCell ref="B32:H32"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C27">
+  <x:conditionalFormatting sqref="C8:C30">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -1052,13 +1124,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C27">
+    <x:dataValidation type="list" sqref="C8:C30">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68ab155a9f634975"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebabb3e371ff4634"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/性能问题.xlsx
+++ b/ProjectProgress/表格/分类进展/性能问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能问题" sheetId="1" r:id="R14cae77f2f5d42eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能问题" sheetId="1" r:id="R2c72563630cb44df"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress8" displayName="CategoryProgress8" ref="A7:H30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H30"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress8" displayName="CategoryProgress8" ref="A7:H33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H33"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-06 09:08:50（北京时间）</x:v>
+        <x:v>更新于 2026-10-07 09:06:54（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,22 +464,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C30,A5)</x:f>
-        <x:v>13</x:v>
+        <x:f>COUNTIF(C8:C33,A5)</x:f>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C30,D5)</x:f>
+        <x:f>COUNTIF(C8:C33,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C30,F5)</x:f>
+        <x:f>COUNTIF(C8:C33,F5)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -544,7 +544,7 @@
       </x:c>
       <x:c r="H8" s="16" t="str"/>
     </x:row>
-    <x:row r="9" ht="126" customHeight="1">
+    <x:row r="9" ht="109" customHeight="1">
       <x:c r="A9" s="7" t="str">
         <x:v>CA-026.03</x:v>
       </x:c>
@@ -555,13 +555,13 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>硬件与旧Shipping39.45应用FPS基线保留。教学楼材质两固定编辑器视角GPU中位变化约1%以内已验；之后新草地42.4万实例无对应帧耗实测。最新月亮/扫射低开销预览恢复不能证明全校园目标达标，仍无完整硬件、画质、像素和路线标准。</x:v>
+        <x:v>旧Shipping39.45应用FPS与教学楼局部材质A/B基线保留。最新150人编辑器固定条件约11.4FPS，对照1人14.7FPS，平均间隔增加20.1ms；草地与最终天气无独立GPU帧耗和显存余量实测，仍缺完整硬件、画质、像素和路线目标。</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>目标待确认；局部材质实测见CA-070.05，草地实际影响见CA-071.06，完整昼夜见CA-064.09。</x:v>
+        <x:v>总体目标待确认；150人对照见CA-072.06，草地影响见CA-071.06、完整昼夜显存见CA-064.09；不能用编辑器帧间隔替代Shipping达标。</x:v>
       </x:c>
       <x:c r="F9" s="14" t="n">
-        <x:v>46300</x:v>
+        <x:v>46301</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
         <x:v>当前夜景与昼夜测试范围</x:v>
@@ -723,13 +723,13 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D16" s="7" t="str">
-        <x:v>旧错峰预算通过但未测渲染帧耗。新月亮高分辨率截图曾耗尽虚拟内存，扫射预览亦显存不足后恢复；测试使用临时低开销预览设置。教学楼材质仅两固定日间视角A/B通过，不能代替完整夜景、昼夜路径和显存余量验收。</x:v>
+        <x:v>旧月亮虚拟内存与扫射显存不足曾恢复。最新天气全场材质重编译亦显存不足，改离线生成后重载、材质和运行检查通过。人群对照只是编辑器帧间隔，仍缺完整昼夜天气路径GPU分项及显存余量验收。</x:v>
       </x:c>
       <x:c r="E16" s="7" t="str">
-        <x:v>整体目标仍见CA-026.03；材质局部实测见CA-070.05，草地实测缺口见CA-071.06。</x:v>
+        <x:v>总体目标见CA-026.03；局部材质、草地与人群各自实测边界分开，恢复运行不证明内存和帧耗目标达标。</x:v>
       </x:c>
       <x:c r="F16" s="14" t="n">
-        <x:v>46300</x:v>
+        <x:v>46301</x:v>
       </x:c>
       <x:c r="G16" s="7" t="str">
         <x:v>昼夜明确未测性能与夜景崩溃恢复记录</x:v>
@@ -1074,45 +1074,117 @@
       </x:c>
       <x:c r="H30" s="16" t="str"/>
     </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="1"/>
-      <x:c r="B31" s="1"/>
-      <x:c r="C31" s="1"/>
-      <x:c r="D31" s="1"/>
-      <x:c r="E31" s="1"/>
-      <x:c r="F31" s="1"/>
-      <x:c r="G31" s="1"/>
-      <x:c r="H31" s="1"/>
-    </x:row>
-    <x:row r="32" ht="34" customHeight="1">
-      <x:c r="A32" s="3" t="str">
+    <x:row r="31" ht="92" customHeight="1">
+      <x:c r="A31" s="7" t="str">
+        <x:v>CA-072</x:v>
+      </x:c>
+      <x:c r="B31" s="7" t="str">
+        <x:v>White四级LOD生成与引用保持</x:v>
+      </x:c>
+      <x:c r="C31" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D31" s="7" t="str">
+        <x:v>四级LOD已生成保存，减面比例1/0.5/0.2/0.08，近处约20.6万渲染顶点、最远约2.2万；LOD0原模型、167根骨骼、眨眼Morph和材质引用保留，回读校验通过。</x:v>
+      </x:c>
+      <x:c r="E31" s="7" t="str">
+        <x:v>完成减面设置与资产校验；实际人群开销见CA-072.06。</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G31" s="7" t="str">
+        <x:v>四级LOD保存和最终聊天交付</x:v>
+      </x:c>
+      <x:c r="H31" s="16" t="str"/>
+    </x:row>
+    <x:row r="32" ht="75" customHeight="1">
+      <x:c r="A32" s="7" t="str">
+        <x:v>CA-072.02</x:v>
+      </x:c>
+      <x:c r="B32" s="7" t="str">
+        <x:v>White屏外行走动画优化策略</x:v>
+      </x:c>
+      <x:c r="C32" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D32" s="7" t="str">
+        <x:v>屏外行走降低骨骼更新开销，可见和休息时恢复完整动画；150人启用，运行中可见完整动画与屏外优化均观测到，稳定策略失配为0。</x:v>
+      </x:c>
+      <x:c r="E32" s="7" t="str">
+        <x:v>可见性切换瞬时计数不等于稳定失配；不据此认定整体帧率达标。</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G32" s="7" t="str">
+        <x:v>150人动画策略运行与保存回读</x:v>
+      </x:c>
+      <x:c r="H32" s="16" t="str"/>
+    </x:row>
+    <x:row r="33" ht="92" customHeight="1">
+      <x:c r="A33" s="7" t="str">
+        <x:v>CA-072.06</x:v>
+      </x:c>
+      <x:c r="B33" s="7" t="str">
+        <x:v>150人与1人编辑器固定条件对照</x:v>
+      </x:c>
+      <x:c r="C33" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D33" s="7" t="str">
+        <x:v>相同编辑器镜头、画质及昼夜时刻，剔除基准脚本工作后的平均间隔：150人88.089ms、1人67.989ms，差20.100ms（+29.56%）；约11.4对14.7FPS。人数和时钟状态最终恢复。</x:v>
+      </x:c>
+      <x:c r="E33" s="7" t="str">
+        <x:v>完成该编辑器帧间隔对照，非独立GPU耗时或Shipping帧率；总体目标见CA-026.03。</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G33" s="7" t="str">
+        <x:v>有效人群基准与最终配置恢复</x:v>
+      </x:c>
+      <x:c r="H33" s="16" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="1"/>
+      <x:c r="B34" s="1"/>
+      <x:c r="C34" s="1"/>
+      <x:c r="D34" s="1"/>
+      <x:c r="E34" s="1"/>
+      <x:c r="F34" s="1"/>
+      <x:c r="G34" s="1"/>
+      <x:c r="H34" s="1"/>
+    </x:row>
+    <x:row r="35" ht="34" customHeight="1">
+      <x:c r="A35" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B32" s="21" t="str">
+      <x:c r="B35" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C32" s="21"/>
-      <x:c r="D32" s="21"/>
-      <x:c r="E32" s="21"/>
-      <x:c r="F32" s="21"/>
-      <x:c r="G32" s="21"/>
-      <x:c r="H32" s="21"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="1"/>
-      <x:c r="B33" s="1"/>
-      <x:c r="C33" s="1"/>
-      <x:c r="D33" s="1"/>
-      <x:c r="E33" s="1"/>
-      <x:c r="F33" s="1"/>
-      <x:c r="G33" s="1"/>
-      <x:c r="H33" s="1"/>
+      <x:c r="C35" s="21"/>
+      <x:c r="D35" s="21"/>
+      <x:c r="E35" s="21"/>
+      <x:c r="F35" s="21"/>
+      <x:c r="G35" s="21"/>
+      <x:c r="H35" s="21"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="1"/>
+      <x:c r="B36" s="1"/>
+      <x:c r="C36" s="1"/>
+      <x:c r="D36" s="1"/>
+      <x:c r="E36" s="1"/>
+      <x:c r="F36" s="1"/>
+      <x:c r="G36" s="1"/>
+      <x:c r="H36" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B32:H32"/>
+    <x:mergeCell ref="B35:H35"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C30">
+  <x:conditionalFormatting sqref="C8:C33">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -1124,13 +1196,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C30">
+    <x:dataValidation type="list" sqref="C8:C33">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebabb3e371ff4634"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c121b7515544ee7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/性能问题.xlsx
+++ b/ProjectProgress/表格/分类进展/性能问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能问题" sheetId="1" r:id="R2c72563630cb44df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能问题" sheetId="1" r:id="Raa35f911e8ff4f78"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -91,7 +91,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -427,7 +433,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-07 09:06:54（北京时间）</x:v>
+        <x:v>更新于 2026-10-09 09:07:22（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -536,8 +542,8 @@
       <x:c r="E8" s="7" t="str">
         <x:v>设置交付见 CA-041、CA-041.02，持久化见 CA-041.03。确认修改后VSM警告和同口径性能结果；光追几何池问题独立见 CA-042。</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="n">
-        <x:v>46298</x:v>
+      <x:c r="F8" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G8" s="7" t="str">
         <x:v>最新远景修复保存交付与VSM历史诊断</x:v>
@@ -560,8 +566,8 @@
       <x:c r="E9" s="7" t="str">
         <x:v>总体目标待确认；150人对照见CA-072.06，草地影响见CA-071.06、完整昼夜显存见CA-064.09；不能用编辑器帧间隔替代Shipping达标。</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F9" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
         <x:v>当前夜景与昼夜测试范围</x:v>
@@ -584,15 +590,15 @@
       <x:c r="E10" s="7" t="str">
         <x:v>用户本次要求只排查。是否实施启动配置 A/B、父映射审计或增量解析仍需决定；不能直接认定引擎缺陷或承诺可消除全部等待。</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="n">
-        <x:v>46295</x:v>
+      <x:c r="F10" s="14" t="d">
+        <x:v>2026-09-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
         <x:v>性能排查报告第 2 节：逐帧任务关联与限制</x:v>
       </x:c>
       <x:c r="H10" s="16" t="str"/>
     </x:row>
-    <x:row r="11" ht="109" customHeight="1">
+    <x:row r="11" ht="92" customHeight="1">
       <x:c r="A11" s="7" t="str">
         <x:v>CA-032.03</x:v>
       </x:c>
@@ -603,16 +609,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
-        <x:v>旧9408组无变化同步135.11秒；全校园9409组135.79秒保留。最新大纲整理9374组全部复用仍耗141.98秒，scan121.316秒，新增夜景同步147.31秒含创建/替换，不可作为无变化A/B。仍无增量缓存实施证据。</x:v>
+        <x:v>保留旧9374组复用141.98秒基线。10月9日食堂最终9052组全部unchanged仍耗155.62秒，scan135.623秒；资产范围有变化，不能直接做耗时优劣A/B，仍缺增量缓存优化交付。</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
-        <x:v>最新无变化等待仍存在；目录整理和新增灯光同步不证明启动优化完成。</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="n">
-        <x:v>46299</x:v>
+        <x:v>当前无变化同步等待仍有实测；9052组验证通过不证明启动等待优化完成。</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
-        <x:v>大纲无变化计时与新增夜景同步边界</x:v>
+        <x:v>save_verification最新9052组复用与时序</x:v>
       </x:c>
       <x:c r="H11" s="16" t="str"/>
     </x:row>
@@ -632,8 +638,8 @@
       <x:c r="E12" s="7" t="str">
         <x:v>保留已交付启动观测。冷缓存、预缓存覆盖与长帧时间关联仍缺证据，确认实施或继续诊断范围。</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="n">
-        <x:v>46297</x:v>
+      <x:c r="F12" s="14" t="d">
+        <x:v>2026-10-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G12" s="7" t="str">
         <x:v>编辑器 PSO 日志及 Shipping 报告第 5、6 节启动边界</x:v>
@@ -656,8 +662,8 @@
       <x:c r="E13" s="7" t="str">
         <x:v>确认是否测导航生成时序和可行走范围；仅在影响被验证后决定碰撞简化，不能把复杂度直接当作已复现帧率主因。</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="n">
-        <x:v>46295</x:v>
+      <x:c r="F13" s="14" t="d">
+        <x:v>2026-09-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G13" s="7" t="str">
         <x:v>性能排查报告第 5 节：导航候选与未验证影响</x:v>
@@ -680,8 +686,8 @@
       <x:c r="E14" s="7" t="str">
         <x:v>当前仅为高负载线索，根因及优化范围仍待确认；如继续诊断，需相同资产、镜头和画质下的可靠逐帧数据。</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="n">
-        <x:v>46297</x:v>
+      <x:c r="F14" s="14" t="d">
+        <x:v>2026-10-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G14" s="7" t="str">
         <x:v>Shipping 报告第 4、6 节资源采样与归因边界</x:v>
@@ -704,15 +710,15 @@
       <x:c r="E15" s="7" t="str">
         <x:v>核对是否实施几何池调整及当前警告；400→1024仍可能触发常驻占比警告。后续远景设置交付不证明此问题已解决。</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="n">
-        <x:v>46297</x:v>
+      <x:c r="F15" s="14" t="d">
+        <x:v>2026-10-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G15" s="7" t="str">
         <x:v>渲染警告聊天诊断最终结果</x:v>
       </x:c>
       <x:c r="H15" s="16" t="str"/>
     </x:row>
-    <x:row r="16" ht="109" customHeight="1">
+    <x:row r="16" ht="126" customHeight="1">
       <x:c r="A16" s="7" t="str">
         <x:v>CA-064.09</x:v>
       </x:c>
@@ -723,16 +729,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D16" s="7" t="str">
-        <x:v>旧月亮虚拟内存与扫射显存不足曾恢复。最新天气全场材质重编译亦显存不足，改离线生成后重载、材质和运行检查通过。人群对照只是编辑器帧间隔，仍缺完整昼夜天气路径GPU分项及显存余量验收。</x:v>
+        <x:v>旧天气/月亮内存问题恢复依据保留。10月8日雨景编译遇内存不足后恢复；10月9日食堂预览遭显存及SK_White硬件光追崩溃，最终会话临时采用软件Lumen并关闭骨骼硬件光追完成画面。仍无完整昼夜天气GPU分项和显存余量验收。</x:v>
       </x:c>
       <x:c r="E16" s="7" t="str">
-        <x:v>总体目标见CA-026.03；局部材质、草地与人群各自实测边界分开，恢复运行不证明内存和帧耗目标达标。</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="n">
-        <x:v>46301</x:v>
+        <x:v>临时编辑器渲染设置不代表持久化或Shipping修复；需按CA-026.03目标核对同环境性能和显存。</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G16" s="7" t="str">
-        <x:v>昼夜明确未测性能与夜景崩溃恢复记录</x:v>
+        <x:v>最新崩溃恢复、DELIVERY临时渲染说明</x:v>
       </x:c>
       <x:c r="H16" s="16" t="str"/>
     </x:row>
@@ -752,8 +758,8 @@
       <x:c r="E17" s="7" t="str">
         <x:v>若需要判定性能影响，核对草地对应实测及CA-026.03目标；不自行运行性能测试。</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F17" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
         <x:v>草地检查范围与局部材质实测时序</x:v>
@@ -778,8 +784,8 @@
       <x:c r="E18" s="7" t="str">
         <x:v>该阶段完成范围为短时编辑器测试；常态约43–45ms，未证明60FPS、打包版或长时间目标达成。</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="n">
-        <x:v>46285</x:v>
+      <x:c r="F18" s="14" t="d">
+        <x:v>2026-09-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G18" s="7" t="str">
         <x:v>体育馆道路优化实测与完整性记录</x:v>
@@ -802,8 +808,8 @@
       <x:c r="E19" s="7" t="str">
         <x:v>保留该阶段优化依据。当前无变化同步和启动等待按 CA-032.03 独立跟踪，不能据此宣称整体同步性能达标。</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="n">
-        <x:v>46295</x:v>
+      <x:c r="F19" s="14" t="d">
+        <x:v>2026-09-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G19" s="7" t="str">
         <x:v>历史内部读取优化结果与 scene 当前完整扫描报告</x:v>
@@ -826,8 +832,8 @@
       <x:c r="E20" s="7" t="str">
         <x:v>把此结果作为固定视角基线；其他视角和实际运行需分别测量。</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="n">
-        <x:v>46292</x:v>
+      <x:c r="F20" s="14" t="d">
+        <x:v>2026-09-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G20" s="7" t="str">
         <x:v>阴影开销实测：有效绘制采样</x:v>
@@ -850,8 +856,8 @@
       <x:c r="E21" s="7" t="str">
         <x:v>编辑器诊断报告交付有效。Shipping 独立实测见 CA-037，两个环境镜头与采样口径不同，不能计算优化倍率。</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="n">
-        <x:v>46296</x:v>
+      <x:c r="F21" s="14" t="d">
+        <x:v>2026-10-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G21" s="7" t="str">
         <x:v>性能聊天 Markdown 格式纠正与上传交付</x:v>
@@ -874,8 +880,8 @@
       <x:c r="E22" s="7" t="str">
         <x:v>基准阶段已完成，仅代表本机、诊断包与该视点。总体目标见 CA-026.03，标准发布和实际显示验收见 CA-038.02、CA-038.03。</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="n">
-        <x:v>46297</x:v>
+      <x:c r="F22" s="14" t="d">
+        <x:v>2026-10-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G22" s="7" t="str">
         <x:v>Shipping 最终聊天与 confirmed_fixed_summary 正式三轮</x:v>
@@ -898,8 +904,8 @@
       <x:c r="E23" s="7" t="str">
         <x:v>本阶段为测试和方案交付，未实施性能修复；后续按新的实施与验收证据更新。</x:v>
       </x:c>
-      <x:c r="F23" s="14" t="n">
-        <x:v>46297</x:v>
+      <x:c r="F23" s="14" t="d">
+        <x:v>2026-10-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G23" s="7" t="str">
         <x:v>最终聊天交付与 git_upload_receipt 远端核对</x:v>
@@ -922,8 +928,8 @@
       <x:c r="E24" s="7" t="str">
         <x:v>设置阶段已交付；收益与警告复测见 CA-026.02，不从设置变更推断帧率提升。</x:v>
       </x:c>
-      <x:c r="F24" s="14" t="n">
-        <x:v>46298</x:v>
+      <x:c r="F24" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G24" s="7" t="str">
         <x:v>远景修复最终交付与 result 设置回读</x:v>
@@ -946,8 +952,8 @@
       <x:c r="E25" s="7" t="str">
         <x:v>遵循用户最终选择。当前没有同镜头A/B或运行路线证明性能收益，另见 CA-026.02。</x:v>
       </x:c>
-      <x:c r="F25" s="14" t="n">
-        <x:v>46298</x:v>
+      <x:c r="F25" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G25" s="7" t="str">
         <x:v>用户直接选择与 result shadow 回读</x:v>
@@ -970,8 +976,8 @@
       <x:c r="E26" s="7" t="str">
         <x:v>设置交付与实测代价分开判断，实测见CA-043.06。</x:v>
       </x:c>
-      <x:c r="F26" s="14" t="n">
-        <x:v>46298</x:v>
+      <x:c r="F26" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G26" s="7" t="str">
         <x:v>风动性能控制完成说明</x:v>
@@ -994,8 +1000,8 @@
       <x:c r="E27" s="7" t="str">
         <x:v>仅编辑器局部A/B，不是Shipping帧率或总体性能达标。</x:v>
       </x:c>
-      <x:c r="F27" s="14" t="n">
-        <x:v>46298</x:v>
+      <x:c r="F27" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G27" s="7" t="str">
         <x:v>最终风动开关性能样本</x:v>
@@ -1018,8 +1024,8 @@
       <x:c r="E28" s="7" t="str">
         <x:v>实现预算已验，不等同整帧性能达标，见CA-064.09。</x:v>
       </x:c>
-      <x:c r="F28" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F28" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G28" s="7" t="str">
         <x:v>runtime_verified与最新修订说明</x:v>
@@ -1042,8 +1048,8 @@
       <x:c r="E29" s="7" t="str">
         <x:v>本项完成局部材质A/B；未代表之后纯色门、草地、所有昼夜或Shipping总体目标。</x:v>
       </x:c>
-      <x:c r="F29" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F29" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G29" s="7" t="str">
         <x:v>材质前后360帧原始数据与限制说明</x:v>
@@ -1066,8 +1072,8 @@
       <x:c r="E30" s="7" t="str">
         <x:v>完成的是控制开销设置，实际帧耗尚未量测见CA-071.06。</x:v>
       </x:c>
-      <x:c r="F30" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F30" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G30" s="7" t="str">
         <x:v>草地布局策略与设置回读</x:v>
@@ -1090,8 +1096,8 @@
       <x:c r="E31" s="7" t="str">
         <x:v>完成减面设置与资产校验；实际人群开销见CA-072.06。</x:v>
       </x:c>
-      <x:c r="F31" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F31" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G31" s="7" t="str">
         <x:v>四级LOD保存和最终聊天交付</x:v>
@@ -1114,8 +1120,8 @@
       <x:c r="E32" s="7" t="str">
         <x:v>可见性切换瞬时计数不等于稳定失配；不据此认定整体帧率达标。</x:v>
       </x:c>
-      <x:c r="F32" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F32" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G32" s="7" t="str">
         <x:v>150人动画策略运行与保存回读</x:v>
@@ -1138,8 +1144,8 @@
       <x:c r="E33" s="7" t="str">
         <x:v>完成该编辑器帧间隔对照，非独立GPU耗时或Shipping帧率；总体目标见CA-026.03。</x:v>
       </x:c>
-      <x:c r="F33" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F33" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G33" s="7" t="str">
         <x:v>有效人群基准与最终配置恢复</x:v>
@@ -1202,7 +1208,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c121b7515544ee7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R518a3f48d12e4f66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/性能问题.xlsx
+++ b/ProjectProgress/表格/分类进展/性能问题.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能问题" sheetId="1" r:id="Raa35f911e8ff4f78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能问题" sheetId="1" r:id="R38eb40de826d4173"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -198,8 +198,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress8" displayName="CategoryProgress8" ref="A7:H33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H33"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress8" displayName="CategoryProgress8" ref="A7:H34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H34"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -433,7 +433,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-09 09:07:22（北京时间）</x:v>
+        <x:v>更新于 2026-10-10 09:11:56（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -470,7 +470,7 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C33,A5)</x:f>
+        <x:f>COUNTIF(C8:C34,A5)</x:f>
         <x:v>16</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
@@ -478,15 +478,15 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C33,D5)</x:f>
+        <x:f>COUNTIF(C8:C34,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C33,F5)</x:f>
-        <x:v>10</x:v>
+        <x:f>COUNTIF(C8:C34,F5)</x:f>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
     </x:row>
@@ -598,7 +598,7 @@
       </x:c>
       <x:c r="H10" s="16" t="str"/>
     </x:row>
-    <x:row r="11" ht="92" customHeight="1">
+    <x:row r="11" ht="109" customHeight="1">
       <x:c r="A11" s="7" t="str">
         <x:v>CA-032.03</x:v>
       </x:c>
@@ -609,16 +609,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
-        <x:v>保留旧9374组复用141.98秒基线。10月9日食堂最终9052组全部unchanged仍耗155.62秒，scan135.623秒；资产范围有变化，不能直接做耗时优劣A/B，仍缺增量缓存优化交付。</x:v>
+        <x:v>旧9374组141.98秒与9052组155.62秒基线保留。10月9日铺装最终8961组全部unchanged仍151.23秒、scan132.197秒。教室合并164.49秒/室内161.12秒含新旧组变更，不能直接作无变化优化A/B；仍无增量优化交付。</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
-        <x:v>当前无变化同步等待仍有实测；9052组验证通过不证明启动等待优化完成。</x:v>
+        <x:v>最新8961组无变化同步仍有等待；验证通过不证明启动等待优化完成，资产范围变化不能直接比较优化倍率。</x:v>
       </x:c>
       <x:c r="F11" s="14" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
-        <x:v>save_verification最新9052组复用与时序</x:v>
+        <x:v>铺装无变化同步与教室有变化同步范围对照</x:v>
       </x:c>
       <x:c r="H11" s="16" t="str"/>
     </x:row>
@@ -718,7 +718,7 @@
       </x:c>
       <x:c r="H15" s="16" t="str"/>
     </x:row>
-    <x:row r="16" ht="126" customHeight="1">
+    <x:row r="16" ht="109" customHeight="1">
       <x:c r="A16" s="7" t="str">
         <x:v>CA-064.09</x:v>
       </x:c>
@@ -729,16 +729,16 @@
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="D16" s="7" t="str">
-        <x:v>旧天气/月亮内存问题恢复依据保留。10月8日雨景编译遇内存不足后恢复；10月9日食堂预览遭显存及SK_White硬件光追崩溃，最终会话临时采用软件Lumen并关闭骨骼硬件光追完成画面。仍无完整昼夜天气GPU分项和显存余量验收。</x:v>
+        <x:v>旧天气/月亮与食堂显存恢复记录保留。10月10日教室材质重编译和高分辨率截图仍触及显存上限，学生光追资源及UV通道查询中断后恢复，最终保存及常规视口交付通过；没有完整昼夜天气GPU分项与显存余量验收。</x:v>
       </x:c>
       <x:c r="E16" s="7" t="str">
-        <x:v>临时编辑器渲染设置不代表持久化或Shipping修复；需按CA-026.03目标核对同环境性能和显存。</x:v>
+        <x:v>教室专项基准缺口见CA-080.10；恢复截图和临时渲染降负载不等于持久化或Shipping显存问题关闭。</x:v>
       </x:c>
       <x:c r="F16" s="14" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G16" s="7" t="str">
-        <x:v>最新崩溃恢复、DELIVERY临时渲染说明</x:v>
+        <x:v>最新教室最终交付限制及恢复摘要</x:v>
       </x:c>
       <x:c r="H16" s="16" t="str"/>
     </x:row>
@@ -766,431 +766,455 @@
       </x:c>
       <x:c r="H17" s="16" t="str"/>
     </x:row>
-    <x:row r="18" ht="109" customHeight="1">
+    <x:row r="18" ht="92" customHeight="1">
       <x:c r="A18" s="7" t="str">
+        <x:v>CA-080.10</x:v>
+      </x:c>
+      <x:c r="B18" s="7" t="str">
+        <x:v>教室改造后帧率及显存影响验收</x:v>
+      </x:c>
+      <x:c r="C18" s="18" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="D18" s="7" t="str">
+        <x:v>共享资产、实例化、简化碰撞与原灯数保持已经交付；最终聊天明确尚未做帧率基准。高分辨率截图多次显存不足，学生光追资源中断，改用常规视口输出最终图。</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="str">
+        <x:v>缺同环境画质、机位和运行范围的帧耗及显存对照；不能从实例数量或不新增灯推断性能达标。</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G18" s="7" t="str">
+        <x:v>最终聊天明确无基准及显存中断</x:v>
+      </x:c>
+      <x:c r="H18" s="16" t="str"/>
+    </x:row>
+    <x:row r="19" ht="109" customHeight="1">
+      <x:c r="A19" s="7" t="str">
         <x:v>CA-025</x:v>
       </x:c>
-      <x:c r="B18" s="7" t="str">
+      <x:c r="B19" s="7" t="str">
         <x:v>体育馆道路植物 Nanite 配置及短时性能改善</x:v>
       </x:c>
-      <x:c r="C18" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D18" s="7" t="str">
+      <x:c r="C19" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D19" s="7" t="str">
         <x:v>11 类优化网格和 54 个材质/父材质资源用于 9,369 个实例，变换与属性校验通过。
 相同视角 GPU 均值：30.57 → 16.35 ms。
 四组共 1,654 帧无超过 100 ms 的长帧，原始资产保留。</x:v>
       </x:c>
-      <x:c r="E18" s="7" t="str">
+      <x:c r="E19" s="7" t="str">
         <x:v>该阶段完成范围为短时编辑器测试；常态约43–45ms，未证明60FPS、打包版或长时间目标达成。</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="d">
+      <x:c r="F19" s="14" t="d">
         <x:v>2026-09-20T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G18" s="7" t="str">
+      <x:c r="G19" s="7" t="str">
         <x:v>体育馆道路优化实测与完整性记录</x:v>
       </x:c>
-      <x:c r="H18" s="16" t="str"/>
-    </x:row>
-    <x:row r="19" ht="126" customHeight="1">
-      <x:c r="A19" s="7" t="str">
+      <x:c r="H19" s="16" t="str"/>
+    </x:row>
+    <x:row r="20" ht="126" customHeight="1">
+      <x:c r="A20" s="7" t="str">
         <x:v>CA-025.02</x:v>
       </x:c>
-      <x:c r="B19" s="7" t="str">
+      <x:c r="B20" s="7" t="str">
         <x:v>保存和 PIE 同步内部读取优化</x:v>
       </x:c>
-      <x:c r="C19" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D19" s="7" t="str">
+      <x:c r="C20" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D20" s="7" t="str">
         <x:v>9 月 20 日保持全场完整扫描的内部读取优化已交付，实际保存同步由 180.87 降至 145.68 秒，10,264 批次和 110,462 实例保持，引用与语法检查通过。9 月 30 日当前场景无变化同步仍为 135.11 秒；旧阶段交付仍有效，增量同步缺口另见 CA-032.03。</x:v>
       </x:c>
-      <x:c r="E19" s="7" t="str">
+      <x:c r="E20" s="7" t="str">
         <x:v>保留该阶段优化依据。当前无变化同步和启动等待按 CA-032.03 独立跟踪，不能据此宣称整体同步性能达标。</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="d">
+      <x:c r="F20" s="14" t="d">
         <x:v>2026-09-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G19" s="7" t="str">
+      <x:c r="G20" s="7" t="str">
         <x:v>历史内部读取优化结果与 scene 当前完整扫描报告</x:v>
       </x:c>
-      <x:c r="H19" s="16" t="str"/>
-    </x:row>
-    <x:row r="20" ht="92" customHeight="1">
-      <x:c r="A20" s="7" t="str">
+      <x:c r="H20" s="16" t="str"/>
+    </x:row>
+    <x:row r="21" ht="92" customHeight="1">
+      <x:c r="A21" s="7" t="str">
         <x:v>CA-026</x:v>
       </x:c>
-      <x:c r="B20" s="7" t="str">
+      <x:c r="B21" s="7" t="str">
         <x:v>固定视角阴影性能基线测量</x:v>
       </x:c>
-      <x:c r="C20" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D20" s="7" t="str">
+      <x:c r="C21" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D21" s="7" t="str">
         <x:v>RTX 4060 Ti 固定编辑器视角开—关—开各 180 帧采样，阴影净 GPU 开销约 2.14 ms/帧、11.8%，显存差约 522 MiB；所有临时设置已恢复。</x:v>
       </x:c>
-      <x:c r="E20" s="7" t="str">
+      <x:c r="E21" s="7" t="str">
         <x:v>把此结果作为固定视角基线；其他视角和实际运行需分别测量。</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="d">
+      <x:c r="F21" s="14" t="d">
         <x:v>2026-09-27T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G20" s="7" t="str">
+      <x:c r="G21" s="7" t="str">
         <x:v>阴影开销实测：有效绘制采样</x:v>
       </x:c>
-      <x:c r="H20" s="16" t="str"/>
-    </x:row>
-    <x:row r="21" ht="126" customHeight="1">
-      <x:c r="A21" s="7" t="str">
+      <x:c r="H21" s="16" t="str"/>
+    </x:row>
+    <x:row r="22" ht="126" customHeight="1">
+      <x:c r="A22" s="7" t="str">
         <x:v>CA-032</x:v>
       </x:c>
-      <x:c r="B21" s="7" t="str">
+      <x:c r="B22" s="7" t="str">
         <x:v>scene 当前性能诊断报告交付</x:v>
       </x:c>
-      <x:c r="C21" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D21" s="7" t="str">
+      <x:c r="C22" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D22" s="7" t="str">
         <x:v>固定编辑器镜头的 340 帧诊断：整帧中位 38.54 ms、主线程 38.47 ms、GPU 13.01 ms，定位 TEDS 等待。10 月 1 日按用户要求转换为 Markdown，结论保留，上传 main 提交 c540e83b047b03ce6476cf720c91eaa6990837b0，替换远端 TXT。</x:v>
       </x:c>
-      <x:c r="E21" s="7" t="str">
+      <x:c r="E22" s="7" t="str">
         <x:v>编辑器诊断报告交付有效。Shipping 独立实测见 CA-037，两个环境镜头与采样口径不同，不能计算优化倍率。</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="d">
+      <x:c r="F22" s="14" t="d">
         <x:v>2026-10-01T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="G21" s="7" t="str">
+      <x:c r="G22" s="7" t="str">
         <x:v>性能聊天 Markdown 格式纠正与上传交付</x:v>
       </x:c>
-      <x:c r="H21" s="16" t="str"/>
-    </x:row>
-    <x:row r="22" ht="109" customHeight="1">
-      <x:c r="A22" s="7" t="str">
+      <x:c r="H22" s="16" t="str"/>
+    </x:row>
+    <x:row r="23" ht="109" customHeight="1">
+      <x:c r="A23" s="7" t="str">
         <x:v>CA-037</x:v>
       </x:c>
-      <x:c r="B22" s="7" t="str">
+      <x:c r="B23" s="7" t="str">
         <x:v>Shipping 诊断包固定视点性能基准</x:v>
       </x:c>
-      <x:c r="C22" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D22" s="7" t="str">
+      <x:c r="C23" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D23" s="7" t="str">
         <x:v>教学楼 A 前同一视点三轮各 60 秒、共 7,095 帧：平均应用 39.45 FPS，P95 34.94 ms，1% low 25.90 FPS；最大 48.26 ms，无 &gt;50 ms 帧。视线转向地面的旧约 60 FPS 样本已排除。</x:v>
       </x:c>
-      <x:c r="E22" s="7" t="str">
+      <x:c r="E23" s="7" t="str">
         <x:v>基准阶段已完成，仅代表本机、诊断包与该视点。总体目标见 CA-026.03，标准发布和实际显示验收见 CA-038.02、CA-038.03。</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="d">
-        <x:v>2026-10-02T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G22" s="7" t="str">
-        <x:v>Shipping 最终聊天与 confirmed_fixed_summary 正式三轮</x:v>
-      </x:c>
-      <x:c r="H22" s="16" t="str"/>
-    </x:row>
-    <x:row r="23" ht="92" customHeight="1">
-      <x:c r="A23" s="7" t="str">
-        <x:v>CA-037.02</x:v>
-      </x:c>
-      <x:c r="B23" s="7" t="str">
-        <x:v>Shipping 实测 Markdown 报告交付</x:v>
-      </x:c>
-      <x:c r="C23" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D23" s="7" t="str">
-        <x:v>报告已保存并上传 main，提交 b6445407d74b6e9425d5b21234041d39d922ae3f；包含正式三轮、启动长帧、构建失败及测量限制。上传凭据核对远端提交与正文和两张截图。</x:v>
-      </x:c>
-      <x:c r="E23" s="7" t="str">
-        <x:v>本阶段为测试和方案交付，未实施性能修复；后续按新的实施与验收证据更新。</x:v>
       </x:c>
       <x:c r="F23" s="14" t="d">
         <x:v>2026-10-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G23" s="7" t="str">
-        <x:v>最终聊天交付与 git_upload_receipt 远端核对</x:v>
+        <x:v>Shipping 最终聊天与 confirmed_fixed_summary 正式三轮</x:v>
       </x:c>
       <x:c r="H23" s="16" t="str"/>
     </x:row>
     <x:row r="24" ht="92" customHeight="1">
       <x:c r="A24" s="7" t="str">
+        <x:v>CA-037.02</x:v>
+      </x:c>
+      <x:c r="B24" s="7" t="str">
+        <x:v>Shipping 实测 Markdown 报告交付</x:v>
+      </x:c>
+      <x:c r="C24" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D24" s="7" t="str">
+        <x:v>报告已保存并上传 main，提交 b6445407d74b6e9425d5b21234041d39d922ae3f；包含正式三轮、启动长帧、构建失败及测量限制。上传凭据核对远端提交与正文和两张截图。</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="str">
+        <x:v>本阶段为测试和方案交付，未实施性能修复；后续按新的实施与验收证据更新。</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="d">
+        <x:v>2026-10-02T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G24" s="7" t="str">
+        <x:v>最终聊天交付与 git_upload_receipt 远端核对</x:v>
+      </x:c>
+      <x:c r="H24" s="16" t="str"/>
+    </x:row>
+    <x:row r="25" ht="92" customHeight="1">
+      <x:c r="A25" s="7" t="str">
         <x:v>CA-041</x:v>
       </x:c>
-      <x:c r="B24" s="7" t="str">
+      <x:c r="B25" s="7" t="str">
         <x:v>scene远景组件禁用Nanite</x:v>
       </x:c>
-      <x:c r="C24" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D24" s="7" t="str">
+      <x:c r="C25" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D25" s="7" t="str">
         <x:v>按用户要求在实例组件上禁用 Nanite。范围为校园外背景城市、远山岛屿、森林和天际线植被，188 个目标组件全部 disallow_nanite=true；原先仅5个组件启用。</x:v>
       </x:c>
-      <x:c r="E24" s="7" t="str">
+      <x:c r="E25" s="7" t="str">
         <x:v>设置阶段已交付；收益与警告复测见 CA-026.02，不从设置变更推断帧率提升。</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="d">
-        <x:v>2026-10-03T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G24" s="7" t="str">
-        <x:v>远景修复最终交付与 result 设置回读</x:v>
-      </x:c>
-      <x:c r="H24" s="16" t="str"/>
-    </x:row>
-    <x:row r="25" ht="75" customHeight="1">
-      <x:c r="A25" s="7" t="str">
-        <x:v>CA-041.02</x:v>
-      </x:c>
-      <x:c r="B25" s="7" t="str">
-        <x:v>scene远景投影关闭</x:v>
-      </x:c>
-      <x:c r="C25" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D25" s="7" t="str">
-        <x:v>用户明确选择完全关闭远景阴影。188 个目标组件的投影及接触阴影已关闭，原先投影的140组件、32,598实例停止投影，scene已保存。</x:v>
-      </x:c>
-      <x:c r="E25" s="7" t="str">
-        <x:v>遵循用户最终选择。当前没有同镜头A/B或运行路线证明性能收益，另见 CA-026.02。</x:v>
       </x:c>
       <x:c r="F25" s="14" t="d">
         <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G25" s="7" t="str">
-        <x:v>用户直接选择与 result shadow 回读</x:v>
+        <x:v>远景修复最终交付与 result 设置回读</x:v>
       </x:c>
       <x:c r="H25" s="16" t="str"/>
     </x:row>
-    <x:row r="26" ht="92" customHeight="1">
+    <x:row r="26" ht="75" customHeight="1">
       <x:c r="A26" s="7" t="str">
-        <x:v>CA-043.04</x:v>
+        <x:v>CA-041.02</x:v>
       </x:c>
       <x:c r="B26" s="7" t="str">
-        <x:v>植被风动距离衰减与远处停算</x:v>
+        <x:v>scene远景投影关闭</x:v>
       </x:c>
       <x:c r="C26" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D26" s="7" t="str">
-        <x:v>已用材质GPU顶点偏移和距离衰减，草18米、草花30米、灌木40米、整树120米、棕榈160米后停止。未增加逐株脚本、骨骼、物理或风动纹理采样。</x:v>
+        <x:v>用户明确选择完全关闭远景阴影。188 个目标组件的投影及接触阴影已关闭，原先投影的140组件、32,598实例停止投影，scene已保存。</x:v>
       </x:c>
       <x:c r="E26" s="7" t="str">
-        <x:v>设置交付与实测代价分开判断，实测见CA-043.06。</x:v>
+        <x:v>遵循用户最终选择。当前没有同镜头A/B或运行路线证明性能收益，另见 CA-026.02。</x:v>
       </x:c>
       <x:c r="F26" s="14" t="d">
         <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G26" s="7" t="str">
-        <x:v>风动性能控制完成说明</x:v>
+        <x:v>用户直接选择与 result shadow 回读</x:v>
       </x:c>
       <x:c r="H26" s="16" t="str"/>
     </x:row>
     <x:row r="27" ht="92" customHeight="1">
       <x:c r="A27" s="7" t="str">
-        <x:v>CA-043.06</x:v>
+        <x:v>CA-043.04</x:v>
       </x:c>
       <x:c r="B27" s="7" t="str">
-        <x:v>植被风动同镜头开关性能测量</x:v>
+        <x:v>植被风动距离衰减与远处停算</x:v>
       </x:c>
       <x:c r="C27" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D27" s="7" t="str">
-        <x:v>编辑器花坛同镜头，关闭和开启各272帧：GPU中位26.57→31.36ms，总帧62.84→62.98ms，风动GPU增加4.79ms；两组各预热5秒、采样约18秒。</x:v>
+        <x:v>已用材质GPU顶点偏移和距离衰减，草18米、草花30米、灌木40米、整树120米、棕榈160米后停止。未增加逐株脚本、骨骼、物理或风动纹理采样。</x:v>
       </x:c>
       <x:c r="E27" s="7" t="str">
-        <x:v>仅编辑器局部A/B，不是Shipping帧率或总体性能达标。</x:v>
+        <x:v>设置交付与实测代价分开判断，实测见CA-043.06。</x:v>
       </x:c>
       <x:c r="F27" s="14" t="d">
         <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G27" s="7" t="str">
-        <x:v>最终风动开关性能样本</x:v>
+        <x:v>风动性能控制完成说明</x:v>
       </x:c>
       <x:c r="H27" s="16" t="str"/>
     </x:row>
     <x:row r="28" ht="92" customHeight="1">
       <x:c r="A28" s="7" t="str">
+        <x:v>CA-043.06</x:v>
+      </x:c>
+      <x:c r="B28" s="7" t="str">
+        <x:v>植被风动同镜头开关性能测量</x:v>
+      </x:c>
+      <x:c r="C28" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D28" s="7" t="str">
+        <x:v>编辑器花坛同镜头，关闭和开启各272帧：GPU中位26.57→31.36ms，总帧62.84→62.98ms，风动GPU增加4.79ms；两组各预热5秒、采样约18秒。</x:v>
+      </x:c>
+      <x:c r="E28" s="7" t="str">
+        <x:v>仅编辑器局部A/B，不是Shipping帧率或总体性能达标。</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G28" s="7" t="str">
+        <x:v>最终风动开关性能样本</x:v>
+      </x:c>
+      <x:c r="H28" s="16" t="str"/>
+    </x:row>
+    <x:row r="29" ht="92" customHeight="1">
+      <x:c r="A29" s="7" t="str">
         <x:v>CA-064.04</x:v>
       </x:c>
-      <x:c r="B28" s="7" t="str">
+      <x:c r="B29" s="7" t="str">
         <x:v>昼夜分批开灯与更新预算实现</x:v>
       </x:c>
-      <x:c r="C28" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D28" s="7" t="str">
+      <x:c r="C29" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D29" s="7" t="str">
         <x:v>保留每帧最多新开4灯（投影灯最多1）、更新16灯预算。默认单灯渐变由6秒放慢至12秒，17:00–19:15错峰窗口约56秒；最新预算及过渡回归通过。</x:v>
       </x:c>
-      <x:c r="E28" s="7" t="str">
+      <x:c r="E29" s="7" t="str">
         <x:v>实现预算已验，不等同整帧性能达标，见CA-064.09。</x:v>
-      </x:c>
-      <x:c r="F28" s="14" t="d">
-        <x:v>2026-10-05T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G28" s="7" t="str">
-        <x:v>runtime_verified与最新修订说明</x:v>
-      </x:c>
-      <x:c r="H28" s="16" t="str"/>
-    </x:row>
-    <x:row r="29" ht="109" customHeight="1">
-      <x:c r="A29" s="7" t="str">
-        <x:v>CA-070.05</x:v>
-      </x:c>
-      <x:c r="B29" s="7" t="str">
-        <x:v>教学楼材质固定视角GPU对比</x:v>
-      </x:c>
-      <x:c r="C29" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D29" s="7" t="str">
-        <x:v>RTX4060Ti编辑器10:30同分辨率，两视角前后各360帧：GPU中位A28.0353→28.0703ms（+0.12%）、B38.5722→38.2128ms（-0.93%）；P95分别32.5221→32.7808、41.3584→41.8701ms。</x:v>
-      </x:c>
-      <x:c r="E29" s="7" t="str">
-        <x:v>本项完成局部材质A/B；未代表之后纯色门、草地、所有昼夜或Shipping总体目标。</x:v>
       </x:c>
       <x:c r="F29" s="14" t="d">
         <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G29" s="7" t="str">
+        <x:v>runtime_verified与最新修订说明</x:v>
+      </x:c>
+      <x:c r="H29" s="16" t="str"/>
+    </x:row>
+    <x:row r="30" ht="109" customHeight="1">
+      <x:c r="A30" s="7" t="str">
+        <x:v>CA-070.05</x:v>
+      </x:c>
+      <x:c r="B30" s="7" t="str">
+        <x:v>教学楼材质固定视角GPU对比</x:v>
+      </x:c>
+      <x:c r="C30" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D30" s="7" t="str">
+        <x:v>RTX4060Ti编辑器10:30同分辨率，两视角前后各360帧：GPU中位A28.0353→28.0703ms（+0.12%）、B38.5722→38.2128ms（-0.93%）；P95分别32.5221→32.7808、41.3584→41.8701ms。</x:v>
+      </x:c>
+      <x:c r="E30" s="7" t="str">
+        <x:v>本项完成局部材质A/B；未代表之后纯色门、草地、所有昼夜或Shipping总体目标。</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G30" s="7" t="str">
         <x:v>材质前后360帧原始数据与限制说明</x:v>
       </x:c>
-      <x:c r="H29" s="16" t="str"/>
-    </x:row>
-    <x:row r="30" ht="75" customHeight="1">
-      <x:c r="A30" s="7" t="str">
+      <x:c r="H30" s="16" t="str"/>
+    </x:row>
+    <x:row r="31" ht="75" customHeight="1">
+      <x:c r="A31" s="7" t="str">
         <x:v>CA-071.04</x:v>
       </x:c>
-      <x:c r="B30" s="7" t="str">
+      <x:c r="B31" s="7" t="str">
         <x:v>密铺草地分块LOD与距离剔除设置</x:v>
       </x:c>
-      <x:c r="C30" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D30" s="7" t="str">
+      <x:c r="C31" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D31" s="7" t="str">
         <x:v>246块约25m范围实例化，三档LOD，35m开始渐隐48m剔除；关闭碰撞导航、动态投影和草地光追可见性，设置验证通过。</x:v>
       </x:c>
-      <x:c r="E30" s="7" t="str">
+      <x:c r="E31" s="7" t="str">
         <x:v>完成的是控制开销设置，实际帧耗尚未量测见CA-071.06。</x:v>
-      </x:c>
-      <x:c r="F30" s="14" t="d">
-        <x:v>2026-10-06T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="G30" s="7" t="str">
-        <x:v>草地布局策略与设置回读</x:v>
-      </x:c>
-      <x:c r="H30" s="16" t="str"/>
-    </x:row>
-    <x:row r="31" ht="92" customHeight="1">
-      <x:c r="A31" s="7" t="str">
-        <x:v>CA-072</x:v>
-      </x:c>
-      <x:c r="B31" s="7" t="str">
-        <x:v>White四级LOD生成与引用保持</x:v>
-      </x:c>
-      <x:c r="C31" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D31" s="7" t="str">
-        <x:v>四级LOD已生成保存，减面比例1/0.5/0.2/0.08，近处约20.6万渲染顶点、最远约2.2万；LOD0原模型、167根骨骼、眨眼Morph和材质引用保留，回读校验通过。</x:v>
-      </x:c>
-      <x:c r="E31" s="7" t="str">
-        <x:v>完成减面设置与资产校验；实际人群开销见CA-072.06。</x:v>
       </x:c>
       <x:c r="F31" s="14" t="d">
         <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G31" s="7" t="str">
-        <x:v>四级LOD保存和最终聊天交付</x:v>
+        <x:v>草地布局策略与设置回读</x:v>
       </x:c>
       <x:c r="H31" s="16" t="str"/>
     </x:row>
-    <x:row r="32" ht="75" customHeight="1">
+    <x:row r="32" ht="92" customHeight="1">
       <x:c r="A32" s="7" t="str">
-        <x:v>CA-072.02</x:v>
+        <x:v>CA-072</x:v>
       </x:c>
       <x:c r="B32" s="7" t="str">
-        <x:v>White屏外行走动画优化策略</x:v>
+        <x:v>White四级LOD生成与引用保持</x:v>
       </x:c>
       <x:c r="C32" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D32" s="7" t="str">
-        <x:v>屏外行走降低骨骼更新开销，可见和休息时恢复完整动画；150人启用，运行中可见完整动画与屏外优化均观测到，稳定策略失配为0。</x:v>
+        <x:v>四级LOD已生成保存，减面比例1/0.5/0.2/0.08，近处约20.6万渲染顶点、最远约2.2万；LOD0原模型、167根骨骼、眨眼Morph和材质引用保留，回读校验通过。</x:v>
       </x:c>
       <x:c r="E32" s="7" t="str">
-        <x:v>可见性切换瞬时计数不等于稳定失配；不据此认定整体帧率达标。</x:v>
+        <x:v>完成减面设置与资产校验；实际人群开销见CA-072.06。</x:v>
       </x:c>
       <x:c r="F32" s="14" t="d">
         <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G32" s="7" t="str">
-        <x:v>150人动画策略运行与保存回读</x:v>
+        <x:v>四级LOD保存和最终聊天交付</x:v>
       </x:c>
       <x:c r="H32" s="16" t="str"/>
     </x:row>
-    <x:row r="33" ht="92" customHeight="1">
+    <x:row r="33" ht="75" customHeight="1">
       <x:c r="A33" s="7" t="str">
-        <x:v>CA-072.06</x:v>
+        <x:v>CA-072.02</x:v>
       </x:c>
       <x:c r="B33" s="7" t="str">
-        <x:v>150人与1人编辑器固定条件对照</x:v>
+        <x:v>White屏外行走动画优化策略</x:v>
       </x:c>
       <x:c r="C33" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D33" s="7" t="str">
-        <x:v>相同编辑器镜头、画质及昼夜时刻，剔除基准脚本工作后的平均间隔：150人88.089ms、1人67.989ms，差20.100ms（+29.56%）；约11.4对14.7FPS。人数和时钟状态最终恢复。</x:v>
+        <x:v>屏外行走降低骨骼更新开销，可见和休息时恢复完整动画；150人启用，运行中可见完整动画与屏外优化均观测到，稳定策略失配为0。</x:v>
       </x:c>
       <x:c r="E33" s="7" t="str">
-        <x:v>完成该编辑器帧间隔对照，非独立GPU耗时或Shipping帧率；总体目标见CA-026.03。</x:v>
+        <x:v>可见性切换瞬时计数不等于稳定失配；不据此认定整体帧率达标。</x:v>
       </x:c>
       <x:c r="F33" s="14" t="d">
         <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G33" s="7" t="str">
+        <x:v>150人动画策略运行与保存回读</x:v>
+      </x:c>
+      <x:c r="H33" s="16" t="str"/>
+    </x:row>
+    <x:row r="34" ht="92" customHeight="1">
+      <x:c r="A34" s="7" t="str">
+        <x:v>CA-072.06</x:v>
+      </x:c>
+      <x:c r="B34" s="7" t="str">
+        <x:v>150人与1人编辑器固定条件对照</x:v>
+      </x:c>
+      <x:c r="C34" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D34" s="7" t="str">
+        <x:v>相同编辑器镜头、画质及昼夜时刻，剔除基准脚本工作后的平均间隔：150人88.089ms、1人67.989ms，差20.100ms（+29.56%）；约11.4对14.7FPS。人数和时钟状态最终恢复。</x:v>
+      </x:c>
+      <x:c r="E34" s="7" t="str">
+        <x:v>完成该编辑器帧间隔对照，非独立GPU耗时或Shipping帧率；总体目标见CA-026.03。</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G34" s="7" t="str">
         <x:v>有效人群基准与最终配置恢复</x:v>
       </x:c>
-      <x:c r="H33" s="16" t="str"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="1"/>
-      <x:c r="B34" s="1"/>
-      <x:c r="C34" s="1"/>
-      <x:c r="D34" s="1"/>
-      <x:c r="E34" s="1"/>
-      <x:c r="F34" s="1"/>
-      <x:c r="G34" s="1"/>
-      <x:c r="H34" s="1"/>
-    </x:row>
-    <x:row r="35" ht="34" customHeight="1">
-      <x:c r="A35" s="3" t="str">
+      <x:c r="H34" s="16" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="1"/>
+      <x:c r="B35" s="1"/>
+      <x:c r="C35" s="1"/>
+      <x:c r="D35" s="1"/>
+      <x:c r="E35" s="1"/>
+      <x:c r="F35" s="1"/>
+      <x:c r="G35" s="1"/>
+      <x:c r="H35" s="1"/>
+    </x:row>
+    <x:row r="36" ht="34" customHeight="1">
+      <x:c r="A36" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B35" s="21" t="str">
+      <x:c r="B36" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C35" s="21"/>
-      <x:c r="D35" s="21"/>
-      <x:c r="E35" s="21"/>
-      <x:c r="F35" s="21"/>
-      <x:c r="G35" s="21"/>
-      <x:c r="H35" s="21"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="1"/>
-      <x:c r="B36" s="1"/>
-      <x:c r="C36" s="1"/>
-      <x:c r="D36" s="1"/>
-      <x:c r="E36" s="1"/>
-      <x:c r="F36" s="1"/>
-      <x:c r="G36" s="1"/>
-      <x:c r="H36" s="1"/>
+      <x:c r="C36" s="21"/>
+      <x:c r="D36" s="21"/>
+      <x:c r="E36" s="21"/>
+      <x:c r="F36" s="21"/>
+      <x:c r="G36" s="21"/>
+      <x:c r="H36" s="21"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="1"/>
+      <x:c r="B37" s="1"/>
+      <x:c r="C37" s="1"/>
+      <x:c r="D37" s="1"/>
+      <x:c r="E37" s="1"/>
+      <x:c r="F37" s="1"/>
+      <x:c r="G37" s="1"/>
+      <x:c r="H37" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B35:H35"/>
+    <x:mergeCell ref="B36:H36"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C33">
+  <x:conditionalFormatting sqref="C8:C34">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -1202,13 +1226,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C33">
+    <x:dataValidation type="list" sqref="C8:C34">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R518a3f48d12e4f66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6711b11422aa4e97"/>
   </x:tableParts>
 </x:worksheet>
 </file>